--- a/Mechanism_info/measurement_info.xlsx
+++ b/Mechanism_info/measurement_info.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u1545774\Documents\GitHub\USOS_shared\Mechanism_info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A4572A-0DFC-4A33-B9AC-AD5C589098E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01153EE7-C0CA-4AB6-A89A-8E3F3A0997E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58875" yWindow="1395" windowWidth="23865" windowHeight="12795" xr2:uid="{698A9B32-3AC5-4EFA-9C0D-28F7A7FA4C52}"/>
+    <workbookView xWindow="11685" yWindow="2813" windowWidth="17145" windowHeight="11835" activeTab="1" xr2:uid="{698A9B32-3AC5-4EFA-9C0D-28F7A7FA4C52}"/>
   </bookViews>
   <sheets>
     <sheet name="Mobile_Lab_Measurements" sheetId="2" r:id="rId1"/>
-    <sheet name="UDAQ_Measurements" sheetId="3" r:id="rId2"/>
-    <sheet name="Combined_Measurements" sheetId="4" r:id="rId3"/>
+    <sheet name="VOC_koh" sheetId="5" r:id="rId2"/>
+    <sheet name="UDAQ_Measurements" sheetId="3" r:id="rId3"/>
+    <sheet name="Combined_Measurements" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="736">
   <si>
     <t>Portable Optical Particle Spectrometer (POPS)</t>
   </si>
@@ -1911,13 +1912,349 @@
   </si>
   <si>
     <t>C8H8</t>
+  </si>
+  <si>
+    <t>IS_VOC</t>
+  </si>
+  <si>
+    <t>kOH (Permar et al., 2023) (10^-12 cm3 molecs-1 s-1</t>
+  </si>
+  <si>
+    <t>Carbon_number</t>
+  </si>
+  <si>
+    <t>Chemical_formula</t>
+  </si>
+  <si>
+    <t>VarName</t>
+  </si>
+  <si>
+    <t>Acetone</t>
+  </si>
+  <si>
+    <t>Acrolein</t>
+  </si>
+  <si>
+    <t>Tetrachloroethylene</t>
+  </si>
+  <si>
+    <t>Trichloroethylene</t>
+  </si>
+  <si>
+    <t>Dichlorodifluoromethane</t>
+  </si>
+  <si>
+    <t>Trichlorofluoromethane</t>
+  </si>
+  <si>
+    <t>Dichloromethane</t>
+  </si>
+  <si>
+    <t>Methyl Bromide</t>
+  </si>
+  <si>
+    <t>Furan</t>
+  </si>
+  <si>
+    <t>Limonene</t>
+  </si>
+  <si>
+    <t>Methacrolein</t>
+  </si>
+  <si>
+    <t>Alpha-pinene</t>
+  </si>
+  <si>
+    <t>Beta-pinene</t>
+  </si>
+  <si>
+    <t>cis-2-butene</t>
+  </si>
+  <si>
+    <t>cis-2-pentene</t>
+  </si>
+  <si>
+    <t>Isopropyl nitrate</t>
+  </si>
+  <si>
+    <t>m/p-Xylene</t>
+  </si>
+  <si>
+    <t>Butane</t>
+  </si>
+  <si>
+    <t>Decane</t>
+  </si>
+  <si>
+    <t>Heptane</t>
+  </si>
+  <si>
+    <t>Hexane</t>
+  </si>
+  <si>
+    <t>Nonane</t>
+  </si>
+  <si>
+    <t>Octane</t>
+  </si>
+  <si>
+    <t>Pentane</t>
+  </si>
+  <si>
+    <t>Propylbenzene</t>
+  </si>
+  <si>
+    <t>Propyl nitrate</t>
+  </si>
+  <si>
+    <t>m/p-Ethyltoluene</t>
+  </si>
+  <si>
+    <t>Methanol</t>
+  </si>
+  <si>
+    <t>Acetonitrile</t>
+  </si>
+  <si>
+    <t>Acetaldehyde</t>
+  </si>
+  <si>
+    <t>Ethanol</t>
+  </si>
+  <si>
+    <t>Methanethiol</t>
+  </si>
+  <si>
+    <t>DMS</t>
+  </si>
+  <si>
+    <t>MVK+MACR</t>
+  </si>
+  <si>
+    <t>Benzaldehyde</t>
+  </si>
+  <si>
+    <t>C8Aromatics</t>
+  </si>
+  <si>
+    <t>C9Aromatics</t>
+  </si>
+  <si>
+    <t>Naphthalene</t>
+  </si>
+  <si>
+    <t>Octanal</t>
+  </si>
+  <si>
+    <t>Monoterpenes</t>
+  </si>
+  <si>
+    <t>Nonanal</t>
+  </si>
+  <si>
+    <t>Formic Acid</t>
+  </si>
+  <si>
+    <t>Tetrachloromethane</t>
+  </si>
+  <si>
+    <t>InUseVOC</t>
+  </si>
+  <si>
+    <t>Grouping1</t>
+  </si>
+  <si>
+    <t>ReasonNotInUse</t>
+  </si>
+  <si>
+    <t>Data Gaps</t>
+  </si>
+  <si>
+    <t>Data issue</t>
+  </si>
+  <si>
+    <t>Using WAS</t>
+  </si>
+  <si>
+    <t>Using PTR</t>
+  </si>
+  <si>
+    <t>Using Ethyl+Xylene WAS</t>
+  </si>
+  <si>
+    <t>Using MVK+MACR PTR</t>
+  </si>
+  <si>
+    <t>Ethyne/Acetylene</t>
+  </si>
+  <si>
+    <t>Propene/Propylene</t>
+  </si>
+  <si>
+    <t>Ethene/Ethylene</t>
+  </si>
+  <si>
+    <t>C10H16</t>
+  </si>
+  <si>
+    <t>C3H6O</t>
+  </si>
+  <si>
+    <t>C3H6O;C3H6O</t>
+  </si>
+  <si>
+    <t>C10H8</t>
+  </si>
+  <si>
+    <t>HCOOH</t>
+  </si>
+  <si>
+    <t>C10H30O5Si5</t>
+  </si>
+  <si>
+    <t>C9H18O</t>
+  </si>
+  <si>
+    <t>C3H4O</t>
+  </si>
+  <si>
+    <t>C2Cl4</t>
+  </si>
+  <si>
+    <t>C2HCl3</t>
+  </si>
+  <si>
+    <t>CCl4</t>
+  </si>
+  <si>
+    <t>CH2Cl2</t>
+  </si>
+  <si>
+    <t>CH3Br</t>
+  </si>
+  <si>
+    <t>C7H6O</t>
+  </si>
+  <si>
+    <t>C2H6S</t>
+  </si>
+  <si>
+    <t>CH3SH</t>
+  </si>
+  <si>
+    <t>C2H5OH</t>
+  </si>
+  <si>
+    <t>CH3CHO</t>
+  </si>
+  <si>
+    <t>CH3CN</t>
+  </si>
+  <si>
+    <t>CH3OH</t>
+  </si>
+  <si>
+    <t>C10H17NO</t>
+  </si>
+  <si>
+    <t>C4H7NO5</t>
+  </si>
+  <si>
+    <t>C5H10O3</t>
+  </si>
+  <si>
+    <t>C8H16O</t>
+  </si>
+  <si>
+    <t>CF2Cl2</t>
+  </si>
+  <si>
+    <t>CFCl3</t>
+  </si>
+  <si>
+    <t>C4H4O</t>
+  </si>
+  <si>
+    <t>C4H6O</t>
+  </si>
+  <si>
+    <t>C3H7NO3</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Other Aldehydes</t>
+  </si>
+  <si>
+    <t>Aromatics</t>
+  </si>
+  <si>
+    <t>Alkenes</t>
+  </si>
+  <si>
+    <t>Organic Acids</t>
+  </si>
+  <si>
+    <t>Alkanes</t>
+  </si>
+  <si>
+    <t>Furanoids</t>
+  </si>
+  <si>
+    <t>C9 Aromatics</t>
+  </si>
+  <si>
+    <t>Solvent</t>
+  </si>
+  <si>
+    <t>Traffic</t>
+  </si>
+  <si>
+    <t>Biogenic</t>
+  </si>
+  <si>
+    <t>C5H9NO5</t>
+  </si>
+  <si>
+    <t>Total concentration of C5 organic nitrates with formula C5H9NO5 in ambient air</t>
+  </si>
+  <si>
+    <t>Isoprene Derived Nitrates</t>
+  </si>
+  <si>
+    <t>D5 siloxane</t>
+  </si>
+  <si>
+    <t>C5 organic nitrates</t>
+  </si>
+  <si>
+    <t>C10 organic nitrates</t>
+  </si>
+  <si>
+    <t>EmissionSource</t>
+  </si>
+  <si>
+    <t>Ethene</t>
+  </si>
+  <si>
+    <t>Propene</t>
+  </si>
+  <si>
+    <t>Butenes</t>
+  </si>
+  <si>
+    <t>Other Alkanes</t>
+  </si>
+  <si>
+    <t>Other Alkenes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1931,16 +2268,33 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1963,13 +2317,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2286,914 +2678,1107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451096C0-28AF-4EBA-9A8D-CDAC8E348A85}">
-  <dimension ref="A1:G191"/>
+  <dimension ref="A1:J191"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27.3984375" customWidth="1"/>
-    <col min="3" max="3" width="19.3984375" customWidth="1"/>
-    <col min="4" max="5" width="13.19921875" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="3" max="4" width="13.19921875" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>519</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>517</v>
+      </c>
       <c r="D1" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G1" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>513</v>
       </c>
       <c r="B2" t="s">
         <v>149</v>
       </c>
+      <c r="C2" t="s">
+        <v>512</v>
+      </c>
       <c r="D2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E2" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="F2" t="s">
-        <v>495</v>
-      </c>
-      <c r="G2" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>510</v>
       </c>
       <c r="B3" t="s">
         <v>149</v>
       </c>
+      <c r="C3" t="s">
+        <v>509</v>
+      </c>
       <c r="D3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E3" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="F3" t="s">
-        <v>495</v>
-      </c>
-      <c r="G3" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>507</v>
       </c>
       <c r="B4" t="s">
         <v>149</v>
       </c>
+      <c r="C4" t="s">
+        <v>506</v>
+      </c>
       <c r="D4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E4" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="F4" t="s">
-        <v>495</v>
-      </c>
-      <c r="G4" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>504</v>
       </c>
       <c r="B5" t="s">
         <v>149</v>
       </c>
+      <c r="C5" t="s">
+        <v>503</v>
+      </c>
       <c r="D5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E5" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="F5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G5" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>501</v>
       </c>
       <c r="B6" t="s">
         <v>149</v>
       </c>
+      <c r="C6" t="s">
+        <v>500</v>
+      </c>
       <c r="D6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E6" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F6" t="s">
-        <v>495</v>
-      </c>
-      <c r="G6" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>498</v>
       </c>
       <c r="B7" t="s">
         <v>149</v>
       </c>
+      <c r="C7" t="s">
+        <v>497</v>
+      </c>
       <c r="D7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F7" t="s">
-        <v>495</v>
-      </c>
-      <c r="G7" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>494</v>
       </c>
       <c r="B8" t="s">
         <v>138</v>
       </c>
-      <c r="E8" t="s">
+      <c r="D8" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>492</v>
       </c>
       <c r="B9" t="s">
         <v>149</v>
       </c>
+      <c r="C9" t="s">
+        <v>491</v>
+      </c>
       <c r="D9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E9" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="F9" t="s">
-        <v>477</v>
-      </c>
-      <c r="G9" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>489</v>
       </c>
       <c r="B10" t="s">
         <v>149</v>
       </c>
+      <c r="C10" t="s">
+        <v>488</v>
+      </c>
       <c r="D10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E10" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="F10" t="s">
-        <v>477</v>
-      </c>
-      <c r="G10" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>486</v>
       </c>
       <c r="B11" t="s">
         <v>149</v>
       </c>
+      <c r="D11" t="s">
+        <v>485</v>
+      </c>
       <c r="E11" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="F11" t="s">
-        <v>477</v>
-      </c>
-      <c r="G11" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>483</v>
       </c>
       <c r="B12" t="s">
         <v>149</v>
       </c>
+      <c r="D12" t="s">
+        <v>482</v>
+      </c>
       <c r="E12" t="s">
-        <v>482</v>
-      </c>
-      <c r="F12" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>481</v>
       </c>
       <c r="B13" t="s">
         <v>149</v>
       </c>
+      <c r="D13" t="s">
+        <v>480</v>
+      </c>
       <c r="E13" t="s">
-        <v>480</v>
-      </c>
-      <c r="F13" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>479</v>
       </c>
       <c r="B14" t="s">
         <v>149</v>
       </c>
+      <c r="D14" t="s">
+        <v>478</v>
+      </c>
       <c r="E14" t="s">
-        <v>478</v>
-      </c>
-      <c r="F14" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>476</v>
       </c>
       <c r="B15" t="s">
         <v>149</v>
       </c>
+      <c r="C15" t="s">
+        <v>475</v>
+      </c>
       <c r="D15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F15" t="s">
-        <v>473</v>
-      </c>
-      <c r="G15" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>472</v>
       </c>
       <c r="B16" t="s">
         <v>149</v>
       </c>
+      <c r="D16" t="s">
+        <v>471</v>
+      </c>
       <c r="E16" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="F16" t="s">
-        <v>462</v>
-      </c>
-      <c r="G16" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>470</v>
       </c>
       <c r="B17" t="s">
         <v>149</v>
       </c>
+      <c r="D17" t="s">
+        <v>469</v>
+      </c>
       <c r="E17" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="F17" t="s">
-        <v>462</v>
-      </c>
-      <c r="G17" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>468</v>
       </c>
       <c r="B18" t="s">
         <v>149</v>
       </c>
+      <c r="D18" t="s">
+        <v>467</v>
+      </c>
       <c r="E18" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F18" t="s">
-        <v>462</v>
-      </c>
-      <c r="G18" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>466</v>
       </c>
       <c r="B19" t="s">
         <v>149</v>
       </c>
+      <c r="D19" t="s">
+        <v>465</v>
+      </c>
       <c r="E19" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F19" t="s">
-        <v>462</v>
-      </c>
-      <c r="G19" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>464</v>
       </c>
       <c r="B20" t="s">
         <v>149</v>
       </c>
+      <c r="D20" t="s">
+        <v>463</v>
+      </c>
       <c r="E20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F20" t="s">
-        <v>462</v>
-      </c>
-      <c r="G20" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>461</v>
       </c>
       <c r="B21" t="s">
         <v>149</v>
       </c>
+      <c r="C21" t="s">
+        <v>460</v>
+      </c>
       <c r="D21" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E21" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F21" t="s">
-        <v>458</v>
-      </c>
-      <c r="G21" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>457</v>
       </c>
       <c r="B22" t="s">
         <v>149</v>
       </c>
+      <c r="C22" t="s">
+        <v>456</v>
+      </c>
       <c r="D22" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E22" t="s">
-        <v>455</v>
+        <v>400</v>
       </c>
       <c r="F22" t="s">
-        <v>400</v>
-      </c>
-      <c r="G22" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>454</v>
       </c>
       <c r="B23" t="s">
         <v>149</v>
       </c>
+      <c r="C23" t="s">
+        <v>453</v>
+      </c>
       <c r="D23" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E23" t="s">
-        <v>452</v>
+        <v>400</v>
       </c>
       <c r="F23" t="s">
-        <v>400</v>
-      </c>
-      <c r="G23" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>451</v>
       </c>
       <c r="B24" t="s">
         <v>149</v>
       </c>
+      <c r="C24" t="s">
+        <v>450</v>
+      </c>
       <c r="D24" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E24" t="s">
-        <v>449</v>
+        <v>400</v>
       </c>
       <c r="F24" t="s">
-        <v>400</v>
-      </c>
-      <c r="G24" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>448</v>
       </c>
       <c r="B25" t="s">
         <v>149</v>
       </c>
+      <c r="C25" t="s">
+        <v>447</v>
+      </c>
       <c r="D25" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E25" t="s">
-        <v>446</v>
+        <v>400</v>
       </c>
       <c r="F25" t="s">
-        <v>400</v>
-      </c>
-      <c r="G25" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>445</v>
       </c>
       <c r="B26" t="s">
         <v>149</v>
       </c>
+      <c r="C26" t="s">
+        <v>444</v>
+      </c>
       <c r="D26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E26" t="s">
-        <v>443</v>
+        <v>400</v>
       </c>
       <c r="F26" t="s">
-        <v>400</v>
-      </c>
-      <c r="G26" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>442</v>
       </c>
       <c r="B27" t="s">
         <v>149</v>
       </c>
+      <c r="C27" t="s">
+        <v>314</v>
+      </c>
       <c r="D27" t="s">
-        <v>314</v>
+        <v>441</v>
       </c>
       <c r="E27" t="s">
-        <v>441</v>
+        <v>400</v>
       </c>
       <c r="F27" t="s">
-        <v>400</v>
-      </c>
-      <c r="G27" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>440</v>
       </c>
       <c r="B28" t="s">
         <v>149</v>
       </c>
+      <c r="D28" t="s">
+        <v>439</v>
+      </c>
       <c r="E28" t="s">
-        <v>439</v>
+        <v>400</v>
       </c>
       <c r="F28" t="s">
-        <v>400</v>
-      </c>
-      <c r="G28" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>438</v>
       </c>
       <c r="B29" t="s">
         <v>149</v>
       </c>
+      <c r="C29" t="s">
+        <v>437</v>
+      </c>
       <c r="D29" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E29" t="s">
-        <v>436</v>
+        <v>400</v>
       </c>
       <c r="F29" t="s">
-        <v>400</v>
-      </c>
-      <c r="G29" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>435</v>
       </c>
       <c r="B30" t="s">
         <v>149</v>
       </c>
+      <c r="C30" t="s">
+        <v>269</v>
+      </c>
       <c r="D30" t="s">
-        <v>269</v>
+        <v>434</v>
       </c>
       <c r="E30" t="s">
-        <v>434</v>
+        <v>400</v>
       </c>
       <c r="F30" t="s">
-        <v>400</v>
-      </c>
-      <c r="G30" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>433</v>
       </c>
       <c r="B31" t="s">
         <v>149</v>
       </c>
+      <c r="D31" t="s">
+        <v>432</v>
+      </c>
       <c r="E31" t="s">
-        <v>432</v>
+        <v>400</v>
       </c>
       <c r="F31" t="s">
-        <v>400</v>
-      </c>
-      <c r="G31" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>431</v>
       </c>
       <c r="B32" t="s">
         <v>149</v>
       </c>
+      <c r="C32" t="s">
+        <v>311</v>
+      </c>
       <c r="D32" t="s">
-        <v>311</v>
+        <v>430</v>
       </c>
       <c r="E32" t="s">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="F32" t="s">
-        <v>400</v>
-      </c>
-      <c r="G32" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>429</v>
       </c>
       <c r="B33" t="s">
         <v>149</v>
       </c>
+      <c r="C33" t="s">
+        <v>248</v>
+      </c>
       <c r="D33" t="s">
-        <v>248</v>
+        <v>428</v>
       </c>
       <c r="E33" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="F33" t="s">
-        <v>400</v>
-      </c>
-      <c r="G33" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>427</v>
       </c>
       <c r="B34" t="s">
         <v>149</v>
       </c>
+      <c r="C34" t="s">
+        <v>426</v>
+      </c>
       <c r="D34" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E34" t="s">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="F34" t="s">
-        <v>400</v>
-      </c>
-      <c r="G34" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>424</v>
       </c>
       <c r="B35" t="s">
         <v>149</v>
       </c>
+      <c r="C35" t="s">
+        <v>423</v>
+      </c>
       <c r="D35" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E35" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="F35" t="s">
-        <v>400</v>
-      </c>
-      <c r="G35" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>421</v>
       </c>
       <c r="B36" t="s">
         <v>149</v>
       </c>
+      <c r="D36" t="s">
+        <v>420</v>
+      </c>
       <c r="E36" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="F36" t="s">
-        <v>400</v>
-      </c>
-      <c r="G36" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>419</v>
       </c>
       <c r="B37" t="s">
         <v>149</v>
       </c>
+      <c r="D37" t="s">
+        <v>418</v>
+      </c>
       <c r="E37" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="F37" t="s">
-        <v>400</v>
-      </c>
-      <c r="G37" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>417</v>
       </c>
       <c r="B38" t="s">
         <v>149</v>
       </c>
+      <c r="C38" t="s">
+        <v>416</v>
+      </c>
       <c r="D38" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E38" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="F38" t="s">
-        <v>400</v>
-      </c>
-      <c r="G38" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>414</v>
       </c>
       <c r="B39" t="s">
         <v>149</v>
       </c>
+      <c r="C39" t="s">
+        <v>413</v>
+      </c>
       <c r="D39" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E39" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="F39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G39" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>411</v>
       </c>
       <c r="B40" t="s">
         <v>149</v>
       </c>
+      <c r="D40" t="s">
+        <v>410</v>
+      </c>
       <c r="E40" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="F40" t="s">
-        <v>400</v>
-      </c>
-      <c r="G40" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>409</v>
       </c>
       <c r="B41" t="s">
         <v>149</v>
       </c>
+      <c r="C41" t="s">
+        <v>408</v>
+      </c>
       <c r="D41" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E41" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="F41" t="s">
-        <v>400</v>
-      </c>
-      <c r="G41" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>406</v>
       </c>
       <c r="B42" t="s">
         <v>149</v>
       </c>
+      <c r="C42" t="s">
+        <v>405</v>
+      </c>
       <c r="D42" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E42" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F42" t="s">
-        <v>400</v>
-      </c>
-      <c r="G42" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>403</v>
       </c>
       <c r="B43" t="s">
         <v>149</v>
       </c>
+      <c r="C43" t="s">
+        <v>402</v>
+      </c>
       <c r="D43" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E43" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F43" t="s">
-        <v>400</v>
-      </c>
-      <c r="G43" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>398</v>
       </c>
       <c r="B44" t="s">
         <v>149</v>
       </c>
+      <c r="C44" t="s">
+        <v>397</v>
+      </c>
       <c r="D44" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E44" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="F44" t="s">
-        <v>389</v>
-      </c>
-      <c r="G44" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>395</v>
       </c>
       <c r="B45" t="s">
         <v>149</v>
       </c>
+      <c r="C45" t="s">
+        <v>394</v>
+      </c>
       <c r="D45" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E45" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F45" t="s">
-        <v>389</v>
-      </c>
-      <c r="G45" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>392</v>
       </c>
       <c r="B46" t="s">
         <v>149</v>
       </c>
+      <c r="C46" t="s">
+        <v>391</v>
+      </c>
       <c r="D46" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E46" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F46" t="s">
-        <v>389</v>
-      </c>
-      <c r="G46" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>388</v>
       </c>
       <c r="B47" t="s">
         <v>149</v>
       </c>
+      <c r="C47" t="s">
+        <v>387</v>
+      </c>
       <c r="D47" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E47" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F47" t="s">
-        <v>385</v>
-      </c>
-      <c r="G47" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>384</v>
       </c>
       <c r="B48" t="s">
         <v>149</v>
       </c>
+      <c r="C48" t="s">
+        <v>383</v>
+      </c>
       <c r="D48" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E48" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F48" t="s">
-        <v>381</v>
-      </c>
-      <c r="G48" t="s">
         <v>380</v>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -3203,17 +3788,20 @@
       <c r="B49" t="s">
         <v>149</v>
       </c>
+      <c r="C49" t="s">
+        <v>378</v>
+      </c>
       <c r="D49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E49" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F49" t="s">
-        <v>376</v>
-      </c>
-      <c r="G49" t="s">
         <v>375</v>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
@@ -3223,14 +3811,17 @@
       <c r="B50" t="s">
         <v>373</v>
       </c>
+      <c r="D50" t="s">
+        <v>372</v>
+      </c>
       <c r="E50" t="s">
-        <v>372</v>
+        <v>141</v>
       </c>
       <c r="F50" t="s">
-        <v>141</v>
-      </c>
-      <c r="G50" t="s">
         <v>359</v>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
@@ -3240,14 +3831,17 @@
       <c r="B51" t="s">
         <v>353</v>
       </c>
+      <c r="D51" t="s">
+        <v>370</v>
+      </c>
       <c r="E51" t="s">
-        <v>370</v>
+        <v>141</v>
       </c>
       <c r="F51" t="s">
-        <v>141</v>
-      </c>
-      <c r="G51" t="s">
         <v>359</v>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
@@ -3257,14 +3851,17 @@
       <c r="B52" t="s">
         <v>350</v>
       </c>
+      <c r="D52" t="s">
+        <v>368</v>
+      </c>
       <c r="E52" t="s">
-        <v>368</v>
+        <v>141</v>
       </c>
       <c r="F52" t="s">
-        <v>141</v>
-      </c>
-      <c r="G52" t="s">
         <v>359</v>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
@@ -3274,14 +3871,17 @@
       <c r="B53" t="s">
         <v>353</v>
       </c>
+      <c r="D53" t="s">
+        <v>366</v>
+      </c>
       <c r="E53" t="s">
-        <v>366</v>
+        <v>141</v>
       </c>
       <c r="F53" t="s">
-        <v>141</v>
-      </c>
-      <c r="G53" t="s">
         <v>359</v>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
@@ -3291,14 +3891,17 @@
       <c r="B54" t="s">
         <v>364</v>
       </c>
+      <c r="D54" t="s">
+        <v>363</v>
+      </c>
       <c r="E54" t="s">
-        <v>363</v>
+        <v>141</v>
       </c>
       <c r="F54" t="s">
-        <v>141</v>
-      </c>
-      <c r="G54" t="s">
         <v>359</v>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
@@ -3308,14 +3911,17 @@
       <c r="B55" t="s">
         <v>361</v>
       </c>
+      <c r="D55" t="s">
+        <v>360</v>
+      </c>
       <c r="E55" t="s">
-        <v>360</v>
+        <v>141</v>
       </c>
       <c r="F55" t="s">
-        <v>141</v>
-      </c>
-      <c r="G55" t="s">
         <v>359</v>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
@@ -3325,14 +3931,17 @@
       <c r="B56" t="s">
         <v>90</v>
       </c>
+      <c r="D56" t="s">
+        <v>357</v>
+      </c>
       <c r="E56" t="s">
-        <v>357</v>
+        <v>141</v>
       </c>
       <c r="F56" t="s">
-        <v>141</v>
-      </c>
-      <c r="G56" t="s">
         <v>348</v>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
@@ -3342,14 +3951,17 @@
       <c r="B57" t="s">
         <v>93</v>
       </c>
+      <c r="D57" t="s">
+        <v>355</v>
+      </c>
       <c r="E57" t="s">
-        <v>355</v>
+        <v>141</v>
       </c>
       <c r="F57" t="s">
-        <v>141</v>
-      </c>
-      <c r="G57" t="s">
         <v>348</v>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
@@ -3359,14 +3971,17 @@
       <c r="B58" t="s">
         <v>353</v>
       </c>
+      <c r="D58" t="s">
+        <v>352</v>
+      </c>
       <c r="E58" t="s">
-        <v>352</v>
+        <v>141</v>
       </c>
       <c r="F58" t="s">
-        <v>141</v>
-      </c>
-      <c r="G58" t="s">
         <v>348</v>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
@@ -3376,14 +3991,17 @@
       <c r="B59" t="s">
         <v>350</v>
       </c>
+      <c r="D59" t="s">
+        <v>349</v>
+      </c>
       <c r="E59" t="s">
-        <v>349</v>
+        <v>141</v>
       </c>
       <c r="F59" t="s">
-        <v>141</v>
-      </c>
-      <c r="G59" t="s">
         <v>348</v>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
@@ -3393,14 +4011,17 @@
       <c r="B60" t="s">
         <v>103</v>
       </c>
+      <c r="D60" t="s">
+        <v>135</v>
+      </c>
       <c r="E60" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="F60" t="s">
-        <v>101</v>
-      </c>
-      <c r="G60" t="s">
         <v>346</v>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
@@ -3410,17 +4031,20 @@
       <c r="B61" t="s">
         <v>149</v>
       </c>
+      <c r="C61" t="s">
+        <v>344</v>
+      </c>
       <c r="D61" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E61" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F61" t="s">
-        <v>335</v>
-      </c>
-      <c r="G61" t="s">
         <v>334</v>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
@@ -3430,17 +4054,20 @@
       <c r="B62" t="s">
         <v>149</v>
       </c>
+      <c r="C62" t="s">
+        <v>326</v>
+      </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="E62" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="F62" t="s">
-        <v>335</v>
-      </c>
-      <c r="G62" t="s">
         <v>334</v>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
@@ -3450,17 +4077,20 @@
       <c r="B63" t="s">
         <v>149</v>
       </c>
+      <c r="C63" t="s">
+        <v>339</v>
+      </c>
       <c r="D63" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E63" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F63" t="s">
-        <v>335</v>
-      </c>
-      <c r="G63" t="s">
         <v>334</v>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
@@ -3470,1285 +4100,1582 @@
       <c r="B64" t="s">
         <v>149</v>
       </c>
+      <c r="C64" t="s">
+        <v>329</v>
+      </c>
       <c r="D64" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="E64" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F64" t="s">
-        <v>335</v>
-      </c>
-      <c r="G64" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>333</v>
       </c>
       <c r="B65" t="s">
         <v>149</v>
       </c>
+      <c r="C65" t="s">
+        <v>332</v>
+      </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E65" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="F65" t="s">
-        <v>324</v>
-      </c>
-      <c r="G65" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>330</v>
       </c>
       <c r="B66" t="s">
         <v>149</v>
       </c>
+      <c r="C66" t="s">
+        <v>329</v>
+      </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E66" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F66" t="s">
-        <v>324</v>
-      </c>
-      <c r="G66" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>327</v>
       </c>
       <c r="B67" t="s">
         <v>149</v>
       </c>
+      <c r="C67" t="s">
+        <v>326</v>
+      </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E67" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F67" t="s">
-        <v>324</v>
-      </c>
-      <c r="G67" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>322</v>
       </c>
       <c r="B68" t="s">
         <v>96</v>
       </c>
+      <c r="D68" t="s">
+        <v>98</v>
+      </c>
       <c r="E68" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="F68" t="s">
-        <v>146</v>
-      </c>
-      <c r="G68" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>321</v>
       </c>
       <c r="B69" t="s">
         <v>96</v>
       </c>
+      <c r="D69" t="s">
+        <v>95</v>
+      </c>
       <c r="E69" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="F69" t="s">
-        <v>146</v>
-      </c>
-      <c r="G69" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>320</v>
       </c>
       <c r="B70" t="s">
         <v>96</v>
       </c>
+      <c r="D70" t="s">
+        <v>319</v>
+      </c>
       <c r="E70" t="s">
-        <v>319</v>
+        <v>146</v>
       </c>
       <c r="F70" t="s">
-        <v>146</v>
-      </c>
-      <c r="G70" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>318</v>
       </c>
       <c r="B71" t="s">
         <v>149</v>
       </c>
+      <c r="C71" t="s">
+        <v>317</v>
+      </c>
       <c r="D71" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E71" t="s">
-        <v>316</v>
+        <v>146</v>
       </c>
       <c r="F71" t="s">
-        <v>146</v>
-      </c>
-      <c r="G71" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>315</v>
       </c>
       <c r="B72" t="s">
         <v>149</v>
       </c>
+      <c r="C72" t="s">
+        <v>314</v>
+      </c>
       <c r="D72" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E72" t="s">
-        <v>313</v>
+        <v>146</v>
       </c>
       <c r="F72" t="s">
-        <v>146</v>
-      </c>
-      <c r="G72" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>312</v>
       </c>
       <c r="B73" t="s">
         <v>149</v>
       </c>
+      <c r="C73" t="s">
+        <v>311</v>
+      </c>
       <c r="D73" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E73" t="s">
-        <v>310</v>
+        <v>146</v>
       </c>
       <c r="F73" t="s">
-        <v>146</v>
-      </c>
-      <c r="G73" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>309</v>
       </c>
       <c r="B74" t="s">
         <v>149</v>
       </c>
+      <c r="C74" t="s">
+        <v>308</v>
+      </c>
       <c r="D74" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E74" t="s">
-        <v>307</v>
+        <v>146</v>
       </c>
       <c r="F74" t="s">
-        <v>146</v>
-      </c>
-      <c r="G74" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>306</v>
       </c>
       <c r="B75" t="s">
         <v>149</v>
       </c>
+      <c r="C75" t="s">
+        <v>305</v>
+      </c>
       <c r="D75" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E75" t="s">
-        <v>304</v>
+        <v>146</v>
       </c>
       <c r="F75" t="s">
-        <v>146</v>
-      </c>
-      <c r="G75" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>303</v>
       </c>
       <c r="B76" t="s">
         <v>149</v>
       </c>
+      <c r="C76" t="s">
+        <v>302</v>
+      </c>
       <c r="D76" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E76" t="s">
-        <v>301</v>
+        <v>146</v>
       </c>
       <c r="F76" t="s">
-        <v>146</v>
-      </c>
-      <c r="G76" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>300</v>
       </c>
       <c r="B77" t="s">
         <v>149</v>
       </c>
+      <c r="C77" t="s">
+        <v>299</v>
+      </c>
       <c r="D77" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E77" t="s">
-        <v>298</v>
+        <v>146</v>
       </c>
       <c r="F77" t="s">
-        <v>146</v>
-      </c>
-      <c r="G77" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>297</v>
       </c>
       <c r="B78" t="s">
         <v>149</v>
       </c>
+      <c r="C78" t="s">
+        <v>296</v>
+      </c>
       <c r="D78" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E78" t="s">
-        <v>295</v>
+        <v>146</v>
       </c>
       <c r="F78" t="s">
-        <v>146</v>
-      </c>
-      <c r="G78" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>294</v>
       </c>
       <c r="B79" t="s">
         <v>149</v>
       </c>
+      <c r="C79" t="s">
+        <v>293</v>
+      </c>
       <c r="D79" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E79" t="s">
-        <v>292</v>
+        <v>146</v>
       </c>
       <c r="F79" t="s">
-        <v>146</v>
-      </c>
-      <c r="G79" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>291</v>
       </c>
       <c r="B80" t="s">
         <v>149</v>
       </c>
+      <c r="C80" t="s">
+        <v>290</v>
+      </c>
       <c r="D80" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E80" t="s">
-        <v>289</v>
+        <v>146</v>
       </c>
       <c r="F80" t="s">
-        <v>146</v>
-      </c>
-      <c r="G80" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>288</v>
       </c>
       <c r="B81" t="s">
         <v>149</v>
       </c>
+      <c r="C81" t="s">
+        <v>287</v>
+      </c>
       <c r="D81" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E81" t="s">
-        <v>286</v>
+        <v>146</v>
       </c>
       <c r="F81" t="s">
-        <v>146</v>
-      </c>
-      <c r="G81" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>285</v>
       </c>
       <c r="B82" t="s">
         <v>149</v>
       </c>
+      <c r="C82" t="s">
+        <v>284</v>
+      </c>
       <c r="D82" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E82" t="s">
-        <v>283</v>
+        <v>146</v>
       </c>
       <c r="F82" t="s">
-        <v>146</v>
-      </c>
-      <c r="G82" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>282</v>
       </c>
       <c r="B83" t="s">
         <v>149</v>
       </c>
+      <c r="C83" t="s">
+        <v>281</v>
+      </c>
       <c r="D83" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E83" t="s">
-        <v>280</v>
+        <v>146</v>
       </c>
       <c r="F83" t="s">
-        <v>146</v>
-      </c>
-      <c r="G83" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>279</v>
       </c>
       <c r="B84" t="s">
         <v>149</v>
       </c>
+      <c r="C84" t="s">
+        <v>278</v>
+      </c>
       <c r="D84" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E84" t="s">
-        <v>277</v>
+        <v>146</v>
       </c>
       <c r="F84" t="s">
-        <v>146</v>
-      </c>
-      <c r="G84" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>276</v>
       </c>
       <c r="B85" t="s">
         <v>149</v>
       </c>
+      <c r="C85" t="s">
+        <v>275</v>
+      </c>
       <c r="D85" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E85" t="s">
-        <v>274</v>
+        <v>146</v>
       </c>
       <c r="F85" t="s">
-        <v>146</v>
-      </c>
-      <c r="G85" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>273</v>
       </c>
       <c r="B86" t="s">
         <v>149</v>
       </c>
+      <c r="C86" t="s">
+        <v>272</v>
+      </c>
       <c r="D86" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E86" t="s">
-        <v>271</v>
+        <v>146</v>
       </c>
       <c r="F86" t="s">
-        <v>146</v>
-      </c>
-      <c r="G86" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>270</v>
       </c>
       <c r="B87" t="s">
         <v>149</v>
       </c>
+      <c r="C87" t="s">
+        <v>269</v>
+      </c>
       <c r="D87" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E87" t="s">
-        <v>268</v>
+        <v>146</v>
       </c>
       <c r="F87" t="s">
-        <v>146</v>
-      </c>
-      <c r="G87" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>162.80000000000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>267</v>
       </c>
       <c r="B88" t="s">
         <v>149</v>
       </c>
+      <c r="C88" t="s">
+        <v>266</v>
+      </c>
       <c r="D88" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E88" t="s">
-        <v>265</v>
+        <v>146</v>
       </c>
       <c r="F88" t="s">
-        <v>146</v>
-      </c>
-      <c r="G88" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>264</v>
       </c>
       <c r="B89" t="s">
         <v>149</v>
       </c>
+      <c r="C89" t="s">
+        <v>263</v>
+      </c>
       <c r="D89" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E89" t="s">
-        <v>262</v>
+        <v>146</v>
       </c>
       <c r="F89" t="s">
-        <v>146</v>
-      </c>
-      <c r="G89" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>261</v>
       </c>
       <c r="B90" t="s">
         <v>149</v>
       </c>
+      <c r="C90" t="s">
+        <v>260</v>
+      </c>
       <c r="D90" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E90" t="s">
-        <v>259</v>
+        <v>146</v>
       </c>
       <c r="F90" t="s">
-        <v>146</v>
-      </c>
-      <c r="G90" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G90" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>258</v>
       </c>
       <c r="B91" t="s">
         <v>149</v>
       </c>
+      <c r="C91" t="s">
+        <v>257</v>
+      </c>
       <c r="D91" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E91" t="s">
-        <v>256</v>
+        <v>146</v>
       </c>
       <c r="F91" t="s">
-        <v>146</v>
-      </c>
-      <c r="G91" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>255</v>
       </c>
       <c r="B92" t="s">
         <v>149</v>
       </c>
+      <c r="C92" t="s">
+        <v>254</v>
+      </c>
       <c r="D92" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E92" t="s">
-        <v>253</v>
+        <v>146</v>
       </c>
       <c r="F92" t="s">
-        <v>146</v>
-      </c>
-      <c r="G92" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G92" t="b">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>252</v>
       </c>
       <c r="B93" t="s">
         <v>149</v>
       </c>
+      <c r="C93" t="s">
+        <v>251</v>
+      </c>
       <c r="D93" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E93" t="s">
-        <v>250</v>
+        <v>146</v>
       </c>
       <c r="F93" t="s">
-        <v>146</v>
-      </c>
-      <c r="G93" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G93" t="b">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>249</v>
       </c>
       <c r="B94" t="s">
         <v>149</v>
       </c>
+      <c r="C94" t="s">
+        <v>248</v>
+      </c>
       <c r="D94" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E94" t="s">
-        <v>247</v>
+        <v>146</v>
       </c>
       <c r="F94" t="s">
-        <v>146</v>
-      </c>
-      <c r="G94" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G94" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>246</v>
       </c>
       <c r="B95" t="s">
         <v>149</v>
       </c>
+      <c r="C95" t="s">
+        <v>245</v>
+      </c>
       <c r="D95" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E95" t="s">
-        <v>244</v>
+        <v>146</v>
       </c>
       <c r="F95" t="s">
-        <v>146</v>
-      </c>
-      <c r="G95" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G95" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95">
+        <v>162.80000000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>243</v>
       </c>
       <c r="B96" t="s">
         <v>149</v>
       </c>
+      <c r="C96" t="s">
+        <v>242</v>
+      </c>
       <c r="D96" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E96" t="s">
-        <v>241</v>
+        <v>146</v>
       </c>
       <c r="F96" t="s">
-        <v>146</v>
-      </c>
-      <c r="G96" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G96" t="b">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>162.80000000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>240</v>
       </c>
       <c r="B97" t="s">
         <v>149</v>
       </c>
+      <c r="C97" t="s">
+        <v>239</v>
+      </c>
       <c r="D97" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E97" t="s">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="F97" t="s">
-        <v>146</v>
-      </c>
-      <c r="G97" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G97" t="b">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>237</v>
       </c>
       <c r="B98" t="s">
         <v>149</v>
       </c>
+      <c r="C98" t="s">
+        <v>236</v>
+      </c>
       <c r="D98" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E98" t="s">
-        <v>235</v>
+        <v>146</v>
       </c>
       <c r="F98" t="s">
-        <v>146</v>
-      </c>
-      <c r="G98" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>234</v>
       </c>
       <c r="B99" t="s">
         <v>149</v>
       </c>
+      <c r="C99" t="s">
+        <v>233</v>
+      </c>
       <c r="D99" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E99" t="s">
-        <v>232</v>
+        <v>146</v>
       </c>
       <c r="F99" t="s">
-        <v>146</v>
-      </c>
-      <c r="G99" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G99" t="b">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>231</v>
       </c>
       <c r="B100" t="s">
         <v>149</v>
       </c>
+      <c r="C100" t="s">
+        <v>230</v>
+      </c>
       <c r="D100" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E100" t="s">
-        <v>229</v>
+        <v>146</v>
       </c>
       <c r="F100" t="s">
-        <v>146</v>
-      </c>
-      <c r="G100" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G100" t="b">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>228</v>
       </c>
       <c r="B101" t="s">
         <v>149</v>
       </c>
+      <c r="C101" t="s">
+        <v>227</v>
+      </c>
       <c r="D101" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E101" t="s">
-        <v>226</v>
+        <v>146</v>
       </c>
       <c r="F101" t="s">
-        <v>146</v>
-      </c>
-      <c r="G101" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>225</v>
       </c>
       <c r="B102" t="s">
         <v>149</v>
       </c>
+      <c r="C102" t="s">
+        <v>224</v>
+      </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E102" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="F102" t="s">
-        <v>146</v>
-      </c>
-      <c r="G102" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G102" t="b">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>222</v>
       </c>
       <c r="B103" t="s">
         <v>149</v>
       </c>
+      <c r="C103" t="s">
+        <v>221</v>
+      </c>
       <c r="D103" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E103" t="s">
-        <v>220</v>
+        <v>146</v>
       </c>
       <c r="F103" t="s">
-        <v>146</v>
-      </c>
-      <c r="G103" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G103" t="b">
+        <v>1</v>
+      </c>
+      <c r="J103">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>219</v>
       </c>
       <c r="B104" t="s">
         <v>149</v>
       </c>
+      <c r="C104" t="s">
+        <v>218</v>
+      </c>
       <c r="D104" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E104" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="F104" t="s">
-        <v>146</v>
-      </c>
-      <c r="G104" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G104" t="b">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>216</v>
       </c>
       <c r="B105" t="s">
         <v>149</v>
       </c>
+      <c r="C105" t="s">
+        <v>215</v>
+      </c>
       <c r="D105" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E105" t="s">
-        <v>214</v>
+        <v>146</v>
       </c>
       <c r="F105" t="s">
-        <v>146</v>
-      </c>
-      <c r="G105" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>213</v>
       </c>
       <c r="B106" t="s">
         <v>149</v>
       </c>
+      <c r="C106" t="s">
+        <v>212</v>
+      </c>
       <c r="D106" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E106" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
       <c r="F106" t="s">
-        <v>146</v>
-      </c>
-      <c r="G106" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G106" t="b">
+        <v>1</v>
+      </c>
+      <c r="J106">
+        <v>7.11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>210</v>
       </c>
       <c r="B107" t="s">
         <v>149</v>
       </c>
+      <c r="C107" t="s">
+        <v>209</v>
+      </c>
       <c r="D107" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E107" t="s">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="F107" t="s">
-        <v>146</v>
-      </c>
-      <c r="G107" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G107" t="b">
+        <v>1</v>
+      </c>
+      <c r="J107">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>207</v>
       </c>
       <c r="B108" t="s">
         <v>149</v>
       </c>
+      <c r="C108" t="s">
+        <v>206</v>
+      </c>
       <c r="D108" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E108" t="s">
-        <v>205</v>
+        <v>146</v>
       </c>
       <c r="F108" t="s">
-        <v>146</v>
-      </c>
-      <c r="G108" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G108" t="b">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>204</v>
       </c>
       <c r="B109" t="s">
         <v>149</v>
       </c>
+      <c r="C109" t="s">
+        <v>203</v>
+      </c>
       <c r="D109" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E109" t="s">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="F109" t="s">
-        <v>146</v>
-      </c>
-      <c r="G109" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G109" t="b">
+        <v>1</v>
+      </c>
+      <c r="J109">
+        <v>8.11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>201</v>
       </c>
       <c r="B110" t="s">
         <v>149</v>
       </c>
+      <c r="C110" t="s">
+        <v>200</v>
+      </c>
       <c r="D110" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E110" t="s">
-        <v>199</v>
+        <v>146</v>
       </c>
       <c r="F110" t="s">
-        <v>146</v>
-      </c>
-      <c r="G110" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G110" t="b">
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>198</v>
       </c>
       <c r="B111" t="s">
         <v>149</v>
       </c>
+      <c r="C111" t="s">
+        <v>197</v>
+      </c>
       <c r="D111" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E111" t="s">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="F111" t="s">
-        <v>146</v>
-      </c>
-      <c r="G111" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>195</v>
       </c>
       <c r="B112" t="s">
         <v>149</v>
       </c>
+      <c r="C112" t="s">
+        <v>194</v>
+      </c>
       <c r="D112" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E112" t="s">
-        <v>193</v>
+        <v>146</v>
       </c>
       <c r="F112" t="s">
-        <v>146</v>
-      </c>
-      <c r="G112" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G112" t="b">
+        <v>1</v>
+      </c>
+      <c r="J112">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>192</v>
       </c>
       <c r="B113" t="s">
         <v>149</v>
       </c>
+      <c r="C113" t="s">
+        <v>191</v>
+      </c>
       <c r="D113" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E113" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="F113" t="s">
-        <v>146</v>
-      </c>
-      <c r="G113" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>189</v>
       </c>
       <c r="B114" t="s">
         <v>149</v>
       </c>
+      <c r="C114" t="s">
+        <v>188</v>
+      </c>
       <c r="D114" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E114" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="F114" t="s">
-        <v>146</v>
-      </c>
-      <c r="G114" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G114" t="b">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>186</v>
       </c>
       <c r="B115" t="s">
         <v>149</v>
       </c>
+      <c r="C115" t="s">
+        <v>185</v>
+      </c>
       <c r="D115" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E115" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="F115" t="s">
-        <v>146</v>
-      </c>
-      <c r="G115" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>183</v>
       </c>
       <c r="B116" t="s">
         <v>149</v>
       </c>
+      <c r="C116" t="s">
+        <v>182</v>
+      </c>
       <c r="D116" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E116" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="F116" t="s">
-        <v>146</v>
-      </c>
-      <c r="G116" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>180</v>
       </c>
       <c r="B117" t="s">
         <v>149</v>
       </c>
+      <c r="C117" t="s">
+        <v>179</v>
+      </c>
       <c r="D117" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E117" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="F117" t="s">
-        <v>146</v>
-      </c>
-      <c r="G117" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>177</v>
       </c>
       <c r="B118" t="s">
         <v>149</v>
       </c>
+      <c r="C118" t="s">
+        <v>176</v>
+      </c>
       <c r="D118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E118" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="F118" t="s">
-        <v>146</v>
-      </c>
-      <c r="G118" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>174</v>
       </c>
       <c r="B119" t="s">
         <v>149</v>
       </c>
+      <c r="C119" t="s">
+        <v>173</v>
+      </c>
       <c r="D119" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E119" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F119" t="s">
-        <v>146</v>
-      </c>
-      <c r="G119" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G119" t="b">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>171</v>
       </c>
       <c r="B120" t="s">
         <v>149</v>
       </c>
+      <c r="C120" t="s">
+        <v>170</v>
+      </c>
       <c r="D120" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E120" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F120" t="s">
-        <v>146</v>
-      </c>
-      <c r="G120" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G120" t="b">
+        <v>1</v>
+      </c>
+      <c r="J120">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>168</v>
       </c>
       <c r="B121" t="s">
         <v>149</v>
       </c>
+      <c r="C121" t="s">
+        <v>167</v>
+      </c>
       <c r="D121" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E121" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="F121" t="s">
-        <v>146</v>
-      </c>
-      <c r="G121" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>165</v>
       </c>
       <c r="B122" t="s">
         <v>149</v>
       </c>
+      <c r="C122" t="s">
+        <v>164</v>
+      </c>
       <c r="D122" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E122" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="F122" t="s">
-        <v>146</v>
-      </c>
-      <c r="G122" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G122" t="b">
+        <v>1</v>
+      </c>
+      <c r="J122">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>162</v>
       </c>
       <c r="B123" t="s">
         <v>149</v>
       </c>
+      <c r="C123" t="s">
+        <v>161</v>
+      </c>
       <c r="D123" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E123" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F123" t="s">
-        <v>146</v>
-      </c>
-      <c r="G123" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G123" t="b">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>159</v>
       </c>
       <c r="B124" t="s">
         <v>149</v>
       </c>
+      <c r="C124" t="s">
+        <v>158</v>
+      </c>
       <c r="D124" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E124" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F124" t="s">
-        <v>146</v>
-      </c>
-      <c r="G124" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>156</v>
       </c>
       <c r="B125" t="s">
         <v>149</v>
       </c>
+      <c r="C125" t="s">
+        <v>155</v>
+      </c>
       <c r="D125" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E125" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F125" t="s">
-        <v>146</v>
-      </c>
-      <c r="G125" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>153</v>
       </c>
       <c r="B126" t="s">
         <v>149</v>
       </c>
+      <c r="C126" t="s">
+        <v>152</v>
+      </c>
       <c r="D126" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E126" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F126" t="s">
-        <v>146</v>
-      </c>
-      <c r="G126" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G126" t="b">
+        <v>1</v>
+      </c>
+      <c r="J126">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>150</v>
       </c>
       <c r="B127" t="s">
         <v>149</v>
       </c>
+      <c r="C127" t="s">
+        <v>148</v>
+      </c>
       <c r="D127" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E127" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F127" t="s">
-        <v>146</v>
-      </c>
-      <c r="G127" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+      <c r="G127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>144</v>
       </c>
       <c r="B128" t="s">
         <v>143</v>
       </c>
+      <c r="D128" t="s">
+        <v>142</v>
+      </c>
       <c r="E128" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F128" t="s">
-        <v>141</v>
-      </c>
-      <c r="G128" t="s">
         <v>140</v>
+      </c>
+      <c r="G128" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.45">
@@ -4758,14 +5685,17 @@
       <c r="B129" t="s">
         <v>138</v>
       </c>
+      <c r="D129" t="s">
+        <v>137</v>
+      </c>
       <c r="E129" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="F129" t="s">
-        <v>101</v>
-      </c>
-      <c r="G129" t="s">
         <v>136</v>
+      </c>
+      <c r="G129" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.45">
@@ -4775,14 +5705,17 @@
       <c r="B130" t="s">
         <v>103</v>
       </c>
+      <c r="D130" t="s">
+        <v>135</v>
+      </c>
       <c r="E130" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="F130" t="s">
-        <v>101</v>
-      </c>
-      <c r="G130" t="s">
         <v>100</v>
+      </c>
+      <c r="G130" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.45">
@@ -4792,14 +5725,17 @@
       <c r="B131" t="s">
         <v>103</v>
       </c>
+      <c r="D131" t="s">
+        <v>133</v>
+      </c>
       <c r="E131" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="F131" t="s">
-        <v>101</v>
-      </c>
-      <c r="G131" t="s">
         <v>100</v>
+      </c>
+      <c r="G131" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.45">
@@ -4809,14 +5745,17 @@
       <c r="B132" t="s">
         <v>103</v>
       </c>
+      <c r="D132" t="s">
+        <v>131</v>
+      </c>
       <c r="E132" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="F132" t="s">
-        <v>101</v>
-      </c>
-      <c r="G132" t="s">
         <v>100</v>
+      </c>
+      <c r="G132" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.45">
@@ -4826,14 +5765,17 @@
       <c r="B133" t="s">
         <v>103</v>
       </c>
+      <c r="D133" t="s">
+        <v>129</v>
+      </c>
       <c r="E133" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="F133" t="s">
-        <v>101</v>
-      </c>
-      <c r="G133" t="s">
         <v>100</v>
+      </c>
+      <c r="G133" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.45">
@@ -4843,14 +5785,17 @@
       <c r="B134" t="s">
         <v>103</v>
       </c>
+      <c r="D134" t="s">
+        <v>127</v>
+      </c>
       <c r="E134" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="F134" t="s">
-        <v>101</v>
-      </c>
-      <c r="G134" t="s">
         <v>100</v>
+      </c>
+      <c r="G134" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.45">
@@ -4860,14 +5805,17 @@
       <c r="B135" t="s">
         <v>103</v>
       </c>
+      <c r="D135" t="s">
+        <v>125</v>
+      </c>
       <c r="E135" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="F135" t="s">
-        <v>101</v>
-      </c>
-      <c r="G135" t="s">
         <v>100</v>
+      </c>
+      <c r="G135" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.45">
@@ -4877,14 +5825,17 @@
       <c r="B136" t="s">
         <v>103</v>
       </c>
+      <c r="D136" t="s">
+        <v>123</v>
+      </c>
       <c r="E136" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="F136" t="s">
-        <v>101</v>
-      </c>
-      <c r="G136" t="s">
         <v>100</v>
+      </c>
+      <c r="G136" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.45">
@@ -4894,14 +5845,17 @@
       <c r="B137" t="s">
         <v>103</v>
       </c>
+      <c r="D137" t="s">
+        <v>121</v>
+      </c>
       <c r="E137" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="F137" t="s">
-        <v>101</v>
-      </c>
-      <c r="G137" t="s">
         <v>100</v>
+      </c>
+      <c r="G137" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.45">
@@ -4911,14 +5865,17 @@
       <c r="B138" t="s">
         <v>103</v>
       </c>
+      <c r="D138" t="s">
+        <v>119</v>
+      </c>
       <c r="E138" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F138" t="s">
-        <v>101</v>
-      </c>
-      <c r="G138" t="s">
         <v>100</v>
+      </c>
+      <c r="G138" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.45">
@@ -4928,14 +5885,17 @@
       <c r="B139" t="s">
         <v>103</v>
       </c>
+      <c r="D139" t="s">
+        <v>117</v>
+      </c>
       <c r="E139" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="F139" t="s">
-        <v>101</v>
-      </c>
-      <c r="G139" t="s">
         <v>100</v>
+      </c>
+      <c r="G139" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.45">
@@ -4945,14 +5905,17 @@
       <c r="B140" t="s">
         <v>103</v>
       </c>
+      <c r="D140" t="s">
+        <v>115</v>
+      </c>
       <c r="E140" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="F140" t="s">
-        <v>101</v>
-      </c>
-      <c r="G140" t="s">
         <v>100</v>
+      </c>
+      <c r="G140" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.45">
@@ -4962,14 +5925,17 @@
       <c r="B141" t="s">
         <v>103</v>
       </c>
+      <c r="D141" t="s">
+        <v>113</v>
+      </c>
       <c r="E141" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F141" t="s">
-        <v>101</v>
-      </c>
-      <c r="G141" t="s">
         <v>100</v>
+      </c>
+      <c r="G141" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.45">
@@ -4979,14 +5945,17 @@
       <c r="B142" t="s">
         <v>103</v>
       </c>
+      <c r="D142" t="s">
+        <v>111</v>
+      </c>
       <c r="E142" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F142" t="s">
-        <v>101</v>
-      </c>
-      <c r="G142" t="s">
         <v>100</v>
+      </c>
+      <c r="G142" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.45">
@@ -4996,14 +5965,17 @@
       <c r="B143" t="s">
         <v>103</v>
       </c>
+      <c r="D143" t="s">
+        <v>109</v>
+      </c>
       <c r="E143" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F143" t="s">
-        <v>101</v>
-      </c>
-      <c r="G143" t="s">
         <v>100</v>
+      </c>
+      <c r="G143" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.45">
@@ -5013,14 +5985,17 @@
       <c r="B144" t="s">
         <v>103</v>
       </c>
+      <c r="D144" t="s">
+        <v>107</v>
+      </c>
       <c r="E144" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F144" t="s">
-        <v>101</v>
-      </c>
-      <c r="G144" t="s">
         <v>100</v>
+      </c>
+      <c r="G144" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.45">
@@ -5030,14 +6005,17 @@
       <c r="B145" t="s">
         <v>103</v>
       </c>
+      <c r="D145" t="s">
+        <v>105</v>
+      </c>
       <c r="E145" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F145" t="s">
-        <v>101</v>
-      </c>
-      <c r="G145" t="s">
         <v>100</v>
+      </c>
+      <c r="G145" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.45">
@@ -5047,14 +6025,17 @@
       <c r="B146" t="s">
         <v>103</v>
       </c>
+      <c r="D146" t="s">
+        <v>102</v>
+      </c>
       <c r="E146" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F146" t="s">
-        <v>101</v>
-      </c>
-      <c r="G146" t="s">
         <v>100</v>
+      </c>
+      <c r="G146" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.45">
@@ -5064,13 +6045,16 @@
       <c r="B147" t="s">
         <v>96</v>
       </c>
+      <c r="D147" t="s">
+        <v>98</v>
+      </c>
       <c r="E147" t="s">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="F147" t="s">
-        <v>1</v>
-      </c>
-      <c r="G147" t="s">
+        <v>0</v>
+      </c>
+      <c r="G147" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5081,13 +6065,16 @@
       <c r="B148" t="s">
         <v>96</v>
       </c>
+      <c r="D148" t="s">
+        <v>95</v>
+      </c>
       <c r="E148" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="F148" t="s">
-        <v>1</v>
-      </c>
-      <c r="G148" t="s">
+        <v>0</v>
+      </c>
+      <c r="G148" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5098,13 +6085,16 @@
       <c r="B149" t="s">
         <v>93</v>
       </c>
+      <c r="D149" t="s">
+        <v>92</v>
+      </c>
       <c r="E149" t="s">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="F149" t="s">
-        <v>1</v>
-      </c>
-      <c r="G149" t="s">
+        <v>0</v>
+      </c>
+      <c r="G149" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5115,13 +6105,16 @@
       <c r="B150" t="s">
         <v>90</v>
       </c>
+      <c r="D150" t="s">
+        <v>89</v>
+      </c>
       <c r="E150" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="F150" t="s">
-        <v>1</v>
-      </c>
-      <c r="G150" t="s">
+        <v>0</v>
+      </c>
+      <c r="G150" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5132,13 +6125,16 @@
       <c r="B151" t="s">
         <v>3</v>
       </c>
+      <c r="D151" t="s">
+        <v>87</v>
+      </c>
       <c r="E151" t="s">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="F151" t="s">
-        <v>1</v>
-      </c>
-      <c r="G151" t="s">
+        <v>0</v>
+      </c>
+      <c r="G151" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5149,13 +6145,16 @@
       <c r="B152" t="s">
         <v>85</v>
       </c>
+      <c r="D152" t="s">
+        <v>84</v>
+      </c>
       <c r="E152" t="s">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="F152" t="s">
-        <v>1</v>
-      </c>
-      <c r="G152" t="s">
+        <v>0</v>
+      </c>
+      <c r="G152" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5166,13 +6165,16 @@
       <c r="B153" t="s">
         <v>82</v>
       </c>
+      <c r="D153" t="s">
+        <v>81</v>
+      </c>
       <c r="E153" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>1</v>
-      </c>
-      <c r="G153" t="s">
+        <v>0</v>
+      </c>
+      <c r="G153" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5183,13 +6185,16 @@
       <c r="B154" t="s">
         <v>79</v>
       </c>
+      <c r="D154" t="s">
+        <v>78</v>
+      </c>
       <c r="E154" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="F154" t="s">
-        <v>1</v>
-      </c>
-      <c r="G154" t="s">
+        <v>0</v>
+      </c>
+      <c r="G154" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5200,13 +6205,16 @@
       <c r="B155" t="s">
         <v>76</v>
       </c>
+      <c r="D155" t="s">
+        <v>75</v>
+      </c>
       <c r="E155" t="s">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="F155" t="s">
-        <v>1</v>
-      </c>
-      <c r="G155" t="s">
+        <v>0</v>
+      </c>
+      <c r="G155" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5217,13 +6225,16 @@
       <c r="B156" t="s">
         <v>3</v>
       </c>
+      <c r="D156" t="s">
+        <v>73</v>
+      </c>
       <c r="E156" t="s">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="F156" t="s">
-        <v>1</v>
-      </c>
-      <c r="G156" t="s">
+        <v>0</v>
+      </c>
+      <c r="G156" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5234,13 +6245,16 @@
       <c r="B157" t="s">
         <v>3</v>
       </c>
+      <c r="D157" t="s">
+        <v>71</v>
+      </c>
       <c r="E157" t="s">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="F157" t="s">
-        <v>1</v>
-      </c>
-      <c r="G157" t="s">
+        <v>0</v>
+      </c>
+      <c r="G157" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5251,13 +6265,16 @@
       <c r="B158" t="s">
         <v>3</v>
       </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
       <c r="E158" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="F158" t="s">
-        <v>1</v>
-      </c>
-      <c r="G158" t="s">
+        <v>0</v>
+      </c>
+      <c r="G158" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5268,13 +6285,16 @@
       <c r="B159" t="s">
         <v>3</v>
       </c>
+      <c r="D159" t="s">
+        <v>67</v>
+      </c>
       <c r="E159" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="F159" t="s">
-        <v>1</v>
-      </c>
-      <c r="G159" t="s">
+        <v>0</v>
+      </c>
+      <c r="G159" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5285,13 +6305,16 @@
       <c r="B160" t="s">
         <v>3</v>
       </c>
+      <c r="D160" t="s">
+        <v>65</v>
+      </c>
       <c r="E160" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="F160" t="s">
-        <v>1</v>
-      </c>
-      <c r="G160" t="s">
+        <v>0</v>
+      </c>
+      <c r="G160" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5302,13 +6325,16 @@
       <c r="B161" t="s">
         <v>3</v>
       </c>
+      <c r="D161" t="s">
+        <v>63</v>
+      </c>
       <c r="E161" t="s">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="F161" t="s">
-        <v>1</v>
-      </c>
-      <c r="G161" t="s">
+        <v>0</v>
+      </c>
+      <c r="G161" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5319,13 +6345,16 @@
       <c r="B162" t="s">
         <v>3</v>
       </c>
+      <c r="D162" t="s">
+        <v>61</v>
+      </c>
       <c r="E162" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F162" t="s">
-        <v>1</v>
-      </c>
-      <c r="G162" t="s">
+        <v>0</v>
+      </c>
+      <c r="G162" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5336,13 +6365,16 @@
       <c r="B163" t="s">
         <v>3</v>
       </c>
+      <c r="D163" t="s">
+        <v>59</v>
+      </c>
       <c r="E163" t="s">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="F163" t="s">
-        <v>1</v>
-      </c>
-      <c r="G163" t="s">
+        <v>0</v>
+      </c>
+      <c r="G163" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5353,13 +6385,16 @@
       <c r="B164" t="s">
         <v>3</v>
       </c>
+      <c r="D164" t="s">
+        <v>57</v>
+      </c>
       <c r="E164" t="s">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="F164" t="s">
-        <v>1</v>
-      </c>
-      <c r="G164" t="s">
+        <v>0</v>
+      </c>
+      <c r="G164" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5370,13 +6405,16 @@
       <c r="B165" t="s">
         <v>3</v>
       </c>
+      <c r="D165" t="s">
+        <v>55</v>
+      </c>
       <c r="E165" t="s">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>1</v>
-      </c>
-      <c r="G165" t="s">
+        <v>0</v>
+      </c>
+      <c r="G165" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5387,13 +6425,16 @@
       <c r="B166" t="s">
         <v>3</v>
       </c>
+      <c r="D166" t="s">
+        <v>53</v>
+      </c>
       <c r="E166" t="s">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>1</v>
-      </c>
-      <c r="G166" t="s">
+        <v>0</v>
+      </c>
+      <c r="G166" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5404,13 +6445,16 @@
       <c r="B167" t="s">
         <v>3</v>
       </c>
+      <c r="D167" t="s">
+        <v>51</v>
+      </c>
       <c r="E167" t="s">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>1</v>
-      </c>
-      <c r="G167" t="s">
+        <v>0</v>
+      </c>
+      <c r="G167" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5421,13 +6465,16 @@
       <c r="B168" t="s">
         <v>3</v>
       </c>
+      <c r="D168" t="s">
+        <v>49</v>
+      </c>
       <c r="E168" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="F168" t="s">
-        <v>1</v>
-      </c>
-      <c r="G168" t="s">
+        <v>0</v>
+      </c>
+      <c r="G168" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5438,13 +6485,16 @@
       <c r="B169" t="s">
         <v>3</v>
       </c>
+      <c r="D169" t="s">
+        <v>47</v>
+      </c>
       <c r="E169" t="s">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="F169" t="s">
-        <v>1</v>
-      </c>
-      <c r="G169" t="s">
+        <v>0</v>
+      </c>
+      <c r="G169" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5455,13 +6505,16 @@
       <c r="B170" t="s">
         <v>3</v>
       </c>
+      <c r="D170" t="s">
+        <v>45</v>
+      </c>
       <c r="E170" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="F170" t="s">
-        <v>1</v>
-      </c>
-      <c r="G170" t="s">
+        <v>0</v>
+      </c>
+      <c r="G170" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5472,13 +6525,16 @@
       <c r="B171" t="s">
         <v>3</v>
       </c>
+      <c r="D171" t="s">
+        <v>43</v>
+      </c>
       <c r="E171" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F171" t="s">
-        <v>1</v>
-      </c>
-      <c r="G171" t="s">
+        <v>0</v>
+      </c>
+      <c r="G171" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5489,13 +6545,16 @@
       <c r="B172" t="s">
         <v>3</v>
       </c>
+      <c r="D172" t="s">
+        <v>41</v>
+      </c>
       <c r="E172" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="F172" t="s">
-        <v>1</v>
-      </c>
-      <c r="G172" t="s">
+        <v>0</v>
+      </c>
+      <c r="G172" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5506,13 +6565,16 @@
       <c r="B173" t="s">
         <v>3</v>
       </c>
+      <c r="D173" t="s">
+        <v>39</v>
+      </c>
       <c r="E173" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="F173" t="s">
-        <v>1</v>
-      </c>
-      <c r="G173" t="s">
+        <v>0</v>
+      </c>
+      <c r="G173" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5523,13 +6585,16 @@
       <c r="B174" t="s">
         <v>3</v>
       </c>
+      <c r="D174" t="s">
+        <v>37</v>
+      </c>
       <c r="E174" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F174" t="s">
-        <v>1</v>
-      </c>
-      <c r="G174" t="s">
+        <v>0</v>
+      </c>
+      <c r="G174" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5540,13 +6605,16 @@
       <c r="B175" t="s">
         <v>3</v>
       </c>
+      <c r="D175" t="s">
+        <v>35</v>
+      </c>
       <c r="E175" t="s">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="F175" t="s">
-        <v>1</v>
-      </c>
-      <c r="G175" t="s">
+        <v>0</v>
+      </c>
+      <c r="G175" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5557,13 +6625,16 @@
       <c r="B176" t="s">
         <v>3</v>
       </c>
+      <c r="D176" t="s">
+        <v>33</v>
+      </c>
       <c r="E176" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F176" t="s">
-        <v>1</v>
-      </c>
-      <c r="G176" t="s">
+        <v>0</v>
+      </c>
+      <c r="G176" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5574,13 +6645,16 @@
       <c r="B177" t="s">
         <v>3</v>
       </c>
+      <c r="D177" t="s">
+        <v>31</v>
+      </c>
       <c r="E177" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F177" t="s">
-        <v>1</v>
-      </c>
-      <c r="G177" t="s">
+        <v>0</v>
+      </c>
+      <c r="G177" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5591,13 +6665,16 @@
       <c r="B178" t="s">
         <v>3</v>
       </c>
+      <c r="D178" t="s">
+        <v>29</v>
+      </c>
       <c r="E178" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>1</v>
-      </c>
-      <c r="G178" t="s">
+        <v>0</v>
+      </c>
+      <c r="G178" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5608,13 +6685,16 @@
       <c r="B179" t="s">
         <v>3</v>
       </c>
+      <c r="D179" t="s">
+        <v>27</v>
+      </c>
       <c r="E179" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F179" t="s">
-        <v>1</v>
-      </c>
-      <c r="G179" t="s">
+        <v>0</v>
+      </c>
+      <c r="G179" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5625,13 +6705,16 @@
       <c r="B180" t="s">
         <v>3</v>
       </c>
+      <c r="D180" t="s">
+        <v>25</v>
+      </c>
       <c r="E180" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F180" t="s">
-        <v>1</v>
-      </c>
-      <c r="G180" t="s">
+        <v>0</v>
+      </c>
+      <c r="G180" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5642,13 +6725,16 @@
       <c r="B181" t="s">
         <v>3</v>
       </c>
+      <c r="D181" t="s">
+        <v>23</v>
+      </c>
       <c r="E181" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F181" t="s">
-        <v>1</v>
-      </c>
-      <c r="G181" t="s">
+        <v>0</v>
+      </c>
+      <c r="G181" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5659,13 +6745,16 @@
       <c r="B182" t="s">
         <v>3</v>
       </c>
+      <c r="D182" t="s">
+        <v>21</v>
+      </c>
       <c r="E182" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F182" t="s">
-        <v>1</v>
-      </c>
-      <c r="G182" t="s">
+        <v>0</v>
+      </c>
+      <c r="G182" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5676,13 +6765,16 @@
       <c r="B183" t="s">
         <v>3</v>
       </c>
+      <c r="D183" t="s">
+        <v>19</v>
+      </c>
       <c r="E183" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F183" t="s">
-        <v>1</v>
-      </c>
-      <c r="G183" t="s">
+        <v>0</v>
+      </c>
+      <c r="G183" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5693,13 +6785,16 @@
       <c r="B184" t="s">
         <v>3</v>
       </c>
+      <c r="D184" t="s">
+        <v>17</v>
+      </c>
       <c r="E184" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F184" t="s">
-        <v>1</v>
-      </c>
-      <c r="G184" t="s">
+        <v>0</v>
+      </c>
+      <c r="G184" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5710,13 +6805,16 @@
       <c r="B185" t="s">
         <v>3</v>
       </c>
+      <c r="D185" t="s">
+        <v>15</v>
+      </c>
       <c r="E185" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F185" t="s">
-        <v>1</v>
-      </c>
-      <c r="G185" t="s">
+        <v>0</v>
+      </c>
+      <c r="G185" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5727,13 +6825,16 @@
       <c r="B186" t="s">
         <v>3</v>
       </c>
+      <c r="D186" t="s">
+        <v>13</v>
+      </c>
       <c r="E186" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F186" t="s">
-        <v>1</v>
-      </c>
-      <c r="G186" t="s">
+        <v>0</v>
+      </c>
+      <c r="G186" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5744,13 +6845,16 @@
       <c r="B187" t="s">
         <v>3</v>
       </c>
+      <c r="D187" t="s">
+        <v>11</v>
+      </c>
       <c r="E187" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F187" t="s">
-        <v>1</v>
-      </c>
-      <c r="G187" t="s">
+        <v>0</v>
+      </c>
+      <c r="G187" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5761,13 +6865,16 @@
       <c r="B188" t="s">
         <v>3</v>
       </c>
+      <c r="D188" t="s">
+        <v>9</v>
+      </c>
       <c r="E188" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F188" t="s">
-        <v>1</v>
-      </c>
-      <c r="G188" t="s">
+        <v>0</v>
+      </c>
+      <c r="G188" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5778,13 +6885,16 @@
       <c r="B189" t="s">
         <v>3</v>
       </c>
+      <c r="D189" t="s">
+        <v>7</v>
+      </c>
       <c r="E189" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>1</v>
-      </c>
-      <c r="G189" t="s">
+        <v>0</v>
+      </c>
+      <c r="G189" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5795,13 +6905,16 @@
       <c r="B190" t="s">
         <v>3</v>
       </c>
+      <c r="D190" t="s">
+        <v>5</v>
+      </c>
       <c r="E190" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>1</v>
-      </c>
-      <c r="G190" t="s">
+        <v>0</v>
+      </c>
+      <c r="G190" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5812,13 +6925,16 @@
       <c r="B191" t="s">
         <v>3</v>
       </c>
+      <c r="D191" t="s">
+        <v>2</v>
+      </c>
       <c r="E191" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>1</v>
-      </c>
-      <c r="G191" t="s">
+        <v>0</v>
+      </c>
+      <c r="G191" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5828,6 +6944,3458 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C25CDB93-1C32-4E52-9A4C-B188A4943EDD}">
+  <dimension ref="A1:O86"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="27.3984375" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="25" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="34.265625" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>705</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" t="s">
+        <v>469</v>
+      </c>
+      <c r="E3" t="s">
+        <v>462</v>
+      </c>
+      <c r="F3" t="s">
+        <v>380</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" t="s">
+        <v>467</v>
+      </c>
+      <c r="E4" t="s">
+        <v>462</v>
+      </c>
+      <c r="F4" t="s">
+        <v>380</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>706</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" t="s">
+        <v>725</v>
+      </c>
+      <c r="E5" t="s">
+        <v>462</v>
+      </c>
+      <c r="F5" t="s">
+        <v>380</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>724</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>464</v>
+      </c>
+      <c r="B6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" t="s">
+        <v>463</v>
+      </c>
+      <c r="E6" t="s">
+        <v>462</v>
+      </c>
+      <c r="F6" t="s">
+        <v>380</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>704</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>457</v>
+      </c>
+      <c r="B7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" t="s">
+        <v>456</v>
+      </c>
+      <c r="D7" t="s">
+        <v>455</v>
+      </c>
+      <c r="E7" t="s">
+        <v>400</v>
+      </c>
+      <c r="F7" t="s">
+        <v>399</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>703</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0.8</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D8" t="s">
+        <v>452</v>
+      </c>
+      <c r="E8" t="s">
+        <v>400</v>
+      </c>
+      <c r="F8" t="s">
+        <v>399</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>702</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D9" t="s">
+        <v>449</v>
+      </c>
+      <c r="E9" t="s">
+        <v>400</v>
+      </c>
+      <c r="F9" t="s">
+        <v>399</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>701</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>15</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>448</v>
+      </c>
+      <c r="B10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" t="s">
+        <v>447</v>
+      </c>
+      <c r="D10" t="s">
+        <v>446</v>
+      </c>
+      <c r="E10" t="s">
+        <v>400</v>
+      </c>
+      <c r="F10" t="s">
+        <v>399</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>700</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>3.2</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>445</v>
+      </c>
+      <c r="B11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" t="s">
+        <v>444</v>
+      </c>
+      <c r="D11" t="s">
+        <v>443</v>
+      </c>
+      <c r="E11" t="s">
+        <v>400</v>
+      </c>
+      <c r="F11" t="s">
+        <v>399</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>699</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" t="s">
+        <v>314</v>
+      </c>
+      <c r="D12" t="s">
+        <v>441</v>
+      </c>
+      <c r="E12" t="s">
+        <v>400</v>
+      </c>
+      <c r="F12" t="s">
+        <v>399</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>691</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+      <c r="J12">
+        <v>20</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>440</v>
+      </c>
+      <c r="B13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" t="s">
+        <v>439</v>
+      </c>
+      <c r="E13" t="s">
+        <v>400</v>
+      </c>
+      <c r="F13" t="s">
+        <v>399</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>686</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>0.2</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>677</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>438</v>
+      </c>
+      <c r="B14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" t="s">
+        <v>437</v>
+      </c>
+      <c r="D14" t="s">
+        <v>436</v>
+      </c>
+      <c r="E14" t="s">
+        <v>400</v>
+      </c>
+      <c r="F14" t="s">
+        <v>399</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>698</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>6</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>435</v>
+      </c>
+      <c r="B15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" t="s">
+        <v>434</v>
+      </c>
+      <c r="E15" t="s">
+        <v>400</v>
+      </c>
+      <c r="F15" t="s">
+        <v>399</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>613</v>
+      </c>
+      <c r="I15">
+        <v>5</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>676</v>
+      </c>
+      <c r="N15" t="s">
+        <v>668</v>
+      </c>
+      <c r="O15" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>433</v>
+      </c>
+      <c r="B16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E16" t="s">
+        <v>400</v>
+      </c>
+      <c r="F16" t="s">
+        <v>399</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="J16">
+        <v>24.8</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>431</v>
+      </c>
+      <c r="B17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" t="s">
+        <v>311</v>
+      </c>
+      <c r="D17" t="s">
+        <v>430</v>
+      </c>
+      <c r="E17" t="s">
+        <v>400</v>
+      </c>
+      <c r="F17" t="s">
+        <v>399</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>619</v>
+      </c>
+      <c r="I17">
+        <v>6</v>
+      </c>
+      <c r="J17">
+        <v>1.2</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="s">
+        <v>715</v>
+      </c>
+      <c r="O17" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>429</v>
+      </c>
+      <c r="B18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" t="s">
+        <v>248</v>
+      </c>
+      <c r="D18" t="s">
+        <v>428</v>
+      </c>
+      <c r="E18" t="s">
+        <v>400</v>
+      </c>
+      <c r="F18" t="s">
+        <v>399</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>620</v>
+      </c>
+      <c r="I18">
+        <v>7</v>
+      </c>
+      <c r="J18">
+        <v>5.6</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="s">
+        <v>715</v>
+      </c>
+      <c r="O18" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>427</v>
+      </c>
+      <c r="B19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" t="s">
+        <v>426</v>
+      </c>
+      <c r="D19" t="s">
+        <v>425</v>
+      </c>
+      <c r="E19" t="s">
+        <v>400</v>
+      </c>
+      <c r="F19" t="s">
+        <v>399</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>623</v>
+      </c>
+      <c r="I19">
+        <v>8</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
+        <v>675</v>
+      </c>
+      <c r="N19" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>424</v>
+      </c>
+      <c r="B20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" t="s">
+        <v>423</v>
+      </c>
+      <c r="D20" t="s">
+        <v>422</v>
+      </c>
+      <c r="E20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F20" t="s">
+        <v>399</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>697</v>
+      </c>
+      <c r="I20">
+        <v>7</v>
+      </c>
+      <c r="J20">
+        <v>12</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="s">
+        <v>675</v>
+      </c>
+      <c r="N20" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>421</v>
+      </c>
+      <c r="B21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" t="s">
+        <v>420</v>
+      </c>
+      <c r="E21" t="s">
+        <v>400</v>
+      </c>
+      <c r="F21" t="s">
+        <v>399</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>618</v>
+      </c>
+      <c r="I21">
+        <v>8</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" t="s">
+        <v>679</v>
+      </c>
+      <c r="N21" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>419</v>
+      </c>
+      <c r="B22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" t="s">
+        <v>418</v>
+      </c>
+      <c r="E22" t="s">
+        <v>400</v>
+      </c>
+      <c r="F22" t="s">
+        <v>399</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>621</v>
+      </c>
+      <c r="I22">
+        <v>9</v>
+      </c>
+      <c r="J22">
+        <v>22</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>417</v>
+      </c>
+      <c r="B23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" t="s">
+        <v>416</v>
+      </c>
+      <c r="D23" t="s">
+        <v>415</v>
+      </c>
+      <c r="E23" t="s">
+        <v>400</v>
+      </c>
+      <c r="F23" t="s">
+        <v>399</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>687</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="s">
+        <v>675</v>
+      </c>
+      <c r="N23" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>414</v>
+      </c>
+      <c r="B24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C24" t="s">
+        <v>413</v>
+      </c>
+      <c r="D24" t="s">
+        <v>412</v>
+      </c>
+      <c r="E24" t="s">
+        <v>400</v>
+      </c>
+      <c r="F24" t="s">
+        <v>399</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>707</v>
+      </c>
+      <c r="I24">
+        <v>8</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>411</v>
+      </c>
+      <c r="B25" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" t="s">
+        <v>410</v>
+      </c>
+      <c r="E25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F25" t="s">
+        <v>399</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>684</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>409</v>
+      </c>
+      <c r="B26" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" t="s">
+        <v>408</v>
+      </c>
+      <c r="D26" t="s">
+        <v>407</v>
+      </c>
+      <c r="E26" t="s">
+        <v>400</v>
+      </c>
+      <c r="F26" t="s">
+        <v>399</v>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>690</v>
+      </c>
+      <c r="I26">
+        <v>9</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>403</v>
+      </c>
+      <c r="B27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D27" t="s">
+        <v>401</v>
+      </c>
+      <c r="E27" t="s">
+        <v>400</v>
+      </c>
+      <c r="F27" t="s">
+        <v>399</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>689</v>
+      </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>388</v>
+      </c>
+      <c r="B28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" t="s">
+        <v>387</v>
+      </c>
+      <c r="D28" t="s">
+        <v>386</v>
+      </c>
+      <c r="E28" t="s">
+        <v>385</v>
+      </c>
+      <c r="F28" t="s">
+        <v>380</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>688</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>0.4</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>333</v>
+      </c>
+      <c r="B29" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" t="s">
+        <v>332</v>
+      </c>
+      <c r="D29" t="s">
+        <v>331</v>
+      </c>
+      <c r="E29" t="s">
+        <v>324</v>
+      </c>
+      <c r="F29" t="s">
+        <v>323</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>616</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>8.5</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>318</v>
+      </c>
+      <c r="B30" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" t="s">
+        <v>317</v>
+      </c>
+      <c r="D30" t="s">
+        <v>316</v>
+      </c>
+      <c r="E30" t="s">
+        <v>146</v>
+      </c>
+      <c r="F30" t="s">
+        <v>145</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>685</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+      <c r="J30">
+        <v>0.2</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>315</v>
+      </c>
+      <c r="B31" t="s">
+        <v>149</v>
+      </c>
+      <c r="C31" t="s">
+        <v>314</v>
+      </c>
+      <c r="D31" t="s">
+        <v>313</v>
+      </c>
+      <c r="E31" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" t="s">
+        <v>145</v>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
+        <v>691</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <v>20</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="s">
+        <v>678</v>
+      </c>
+      <c r="N31" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>312</v>
+      </c>
+      <c r="B32" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" t="s">
+        <v>311</v>
+      </c>
+      <c r="D32" t="s">
+        <v>310</v>
+      </c>
+      <c r="E32" t="s">
+        <v>146</v>
+      </c>
+      <c r="F32" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>619</v>
+      </c>
+      <c r="I32">
+        <v>6</v>
+      </c>
+      <c r="J32">
+        <v>1.2</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="s">
+        <v>678</v>
+      </c>
+      <c r="N32" t="s">
+        <v>715</v>
+      </c>
+      <c r="O32" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>309</v>
+      </c>
+      <c r="B33" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" t="s">
+        <v>308</v>
+      </c>
+      <c r="D33" t="s">
+        <v>307</v>
+      </c>
+      <c r="E33" t="s">
+        <v>146</v>
+      </c>
+      <c r="F33" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>692</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>306</v>
+      </c>
+      <c r="B34" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" t="s">
+        <v>305</v>
+      </c>
+      <c r="D34" t="s">
+        <v>304</v>
+      </c>
+      <c r="E34" t="s">
+        <v>146</v>
+      </c>
+      <c r="F34" t="s">
+        <v>145</v>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
+        <v>693</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>303</v>
+      </c>
+      <c r="B35" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" t="s">
+        <v>302</v>
+      </c>
+      <c r="D35" t="s">
+        <v>301</v>
+      </c>
+      <c r="E35" t="s">
+        <v>146</v>
+      </c>
+      <c r="F35" t="s">
+        <v>145</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
+        <v>694</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>300</v>
+      </c>
+      <c r="B36" t="s">
+        <v>149</v>
+      </c>
+      <c r="C36" t="s">
+        <v>299</v>
+      </c>
+      <c r="D36" t="s">
+        <v>298</v>
+      </c>
+      <c r="E36" t="s">
+        <v>146</v>
+      </c>
+      <c r="F36" t="s">
+        <v>145</v>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="s">
+        <v>708</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>297</v>
+      </c>
+      <c r="B37" t="s">
+        <v>149</v>
+      </c>
+      <c r="C37" t="s">
+        <v>296</v>
+      </c>
+      <c r="D37" t="s">
+        <v>295</v>
+      </c>
+      <c r="E37" t="s">
+        <v>146</v>
+      </c>
+      <c r="F37" t="s">
+        <v>145</v>
+      </c>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" t="s">
+        <v>709</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" s="6" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>294</v>
+      </c>
+      <c r="B38" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" t="s">
+        <v>293</v>
+      </c>
+      <c r="D38" t="s">
+        <v>292</v>
+      </c>
+      <c r="E38" t="s">
+        <v>146</v>
+      </c>
+      <c r="F38" t="s">
+        <v>145</v>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" t="s">
+        <v>695</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="O38" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>291</v>
+      </c>
+      <c r="B39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C39" t="s">
+        <v>290</v>
+      </c>
+      <c r="D39" t="s">
+        <v>289</v>
+      </c>
+      <c r="E39" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" t="s">
+        <v>145</v>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="s">
+        <v>696</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="L39" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>288</v>
+      </c>
+      <c r="B40" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40" t="s">
+        <v>287</v>
+      </c>
+      <c r="D40" t="s">
+        <v>286</v>
+      </c>
+      <c r="E40" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" t="s">
+        <v>145</v>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>607</v>
+      </c>
+      <c r="I40">
+        <v>5</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>285</v>
+      </c>
+      <c r="B41" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" t="s">
+        <v>284</v>
+      </c>
+      <c r="D41" t="s">
+        <v>283</v>
+      </c>
+      <c r="E41" t="s">
+        <v>146</v>
+      </c>
+      <c r="F41" t="s">
+        <v>145</v>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>618</v>
+      </c>
+      <c r="I41">
+        <v>8</v>
+      </c>
+      <c r="J41">
+        <v>13.2</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
+      <c r="N41" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>282</v>
+      </c>
+      <c r="B42" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" t="s">
+        <v>281</v>
+      </c>
+      <c r="D42" t="s">
+        <v>280</v>
+      </c>
+      <c r="E42" t="s">
+        <v>146</v>
+      </c>
+      <c r="F42" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>598</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42">
+        <v>0.24</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+      <c r="N42" s="7" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>279</v>
+      </c>
+      <c r="B43" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" t="s">
+        <v>278</v>
+      </c>
+      <c r="D43" t="s">
+        <v>277</v>
+      </c>
+      <c r="E43" t="s">
+        <v>146</v>
+      </c>
+      <c r="F43" t="s">
+        <v>145</v>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>599</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43">
+        <v>7.8</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="N43" s="7" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>276</v>
+      </c>
+      <c r="B44" t="s">
+        <v>149</v>
+      </c>
+      <c r="C44" t="s">
+        <v>275</v>
+      </c>
+      <c r="D44" t="s">
+        <v>274</v>
+      </c>
+      <c r="E44" t="s">
+        <v>146</v>
+      </c>
+      <c r="F44" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>602</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>681</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>273</v>
+      </c>
+      <c r="B45" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" t="s">
+        <v>272</v>
+      </c>
+      <c r="D45" t="s">
+        <v>271</v>
+      </c>
+      <c r="E45" t="s">
+        <v>146</v>
+      </c>
+      <c r="F45" t="s">
+        <v>145</v>
+      </c>
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>710</v>
+      </c>
+      <c r="I45">
+        <v>4</v>
+      </c>
+      <c r="J45">
+        <v>40</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" s="7" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>270</v>
+      </c>
+      <c r="B46" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" t="s">
+        <v>269</v>
+      </c>
+      <c r="D46" t="s">
+        <v>268</v>
+      </c>
+      <c r="E46" t="s">
+        <v>146</v>
+      </c>
+      <c r="F46" t="s">
+        <v>145</v>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>613</v>
+      </c>
+      <c r="I46">
+        <v>5</v>
+      </c>
+      <c r="J46">
+        <v>162.80000000000001</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+      <c r="N46" t="s">
+        <v>668</v>
+      </c>
+      <c r="O46" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>267</v>
+      </c>
+      <c r="B47" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" t="s">
+        <v>266</v>
+      </c>
+      <c r="D47" t="s">
+        <v>265</v>
+      </c>
+      <c r="E47" t="s">
+        <v>146</v>
+      </c>
+      <c r="F47" t="s">
+        <v>145</v>
+      </c>
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>19</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>668</v>
+      </c>
+      <c r="O47" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>264</v>
+      </c>
+      <c r="B48" t="s">
+        <v>149</v>
+      </c>
+      <c r="C48" t="s">
+        <v>263</v>
+      </c>
+      <c r="D48" t="s">
+        <v>262</v>
+      </c>
+      <c r="E48" t="s">
+        <v>146</v>
+      </c>
+      <c r="F48" t="s">
+        <v>145</v>
+      </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>711</v>
+      </c>
+      <c r="I48">
+        <v>4</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="s">
+        <v>680</v>
+      </c>
+      <c r="N48" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>261</v>
+      </c>
+      <c r="B49" t="s">
+        <v>149</v>
+      </c>
+      <c r="C49" t="s">
+        <v>260</v>
+      </c>
+      <c r="D49" t="s">
+        <v>259</v>
+      </c>
+      <c r="E49" t="s">
+        <v>146</v>
+      </c>
+      <c r="F49" t="s">
+        <v>145</v>
+      </c>
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H49" t="s">
+        <v>615</v>
+      </c>
+      <c r="I49">
+        <v>7</v>
+      </c>
+      <c r="J49">
+        <v>11</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>258</v>
+      </c>
+      <c r="B50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D50" t="s">
+        <v>256</v>
+      </c>
+      <c r="E50" t="s">
+        <v>146</v>
+      </c>
+      <c r="F50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G50" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" t="s">
+        <v>614</v>
+      </c>
+      <c r="I50">
+        <v>6</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>255</v>
+      </c>
+      <c r="B51" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" t="s">
+        <v>254</v>
+      </c>
+      <c r="D51" t="s">
+        <v>253</v>
+      </c>
+      <c r="E51" t="s">
+        <v>146</v>
+      </c>
+      <c r="F51" t="s">
+        <v>145</v>
+      </c>
+      <c r="G51" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
+        <v>600</v>
+      </c>
+      <c r="I51">
+        <v>3</v>
+      </c>
+      <c r="J51">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>252</v>
+      </c>
+      <c r="B52" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52" t="s">
+        <v>251</v>
+      </c>
+      <c r="D52" t="s">
+        <v>250</v>
+      </c>
+      <c r="E52" t="s">
+        <v>146</v>
+      </c>
+      <c r="F52" t="s">
+        <v>145</v>
+      </c>
+      <c r="G52" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" t="s">
+        <v>601</v>
+      </c>
+      <c r="I52">
+        <v>3</v>
+      </c>
+      <c r="J52">
+        <v>30</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" s="7" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>249</v>
+      </c>
+      <c r="B53" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" t="s">
+        <v>248</v>
+      </c>
+      <c r="D53" t="s">
+        <v>247</v>
+      </c>
+      <c r="E53" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" t="s">
+        <v>145</v>
+      </c>
+      <c r="G53" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>620</v>
+      </c>
+      <c r="I53">
+        <v>7</v>
+      </c>
+      <c r="J53">
+        <v>5.6</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="s">
+        <v>678</v>
+      </c>
+      <c r="N53" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>246</v>
+      </c>
+      <c r="B54" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" t="s">
+        <v>245</v>
+      </c>
+      <c r="D54" t="s">
+        <v>244</v>
+      </c>
+      <c r="E54" t="s">
+        <v>146</v>
+      </c>
+      <c r="F54" t="s">
+        <v>145</v>
+      </c>
+      <c r="G54" t="b">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>684</v>
+      </c>
+      <c r="I54">
+        <v>10</v>
+      </c>
+      <c r="J54">
+        <v>162.80000000000001</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" t="s">
+        <v>668</v>
+      </c>
+      <c r="O54" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>243</v>
+      </c>
+      <c r="B55" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" t="s">
+        <v>242</v>
+      </c>
+      <c r="D55" t="s">
+        <v>241</v>
+      </c>
+      <c r="E55" t="s">
+        <v>146</v>
+      </c>
+      <c r="F55" t="s">
+        <v>145</v>
+      </c>
+      <c r="G55" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" t="s">
+        <v>684</v>
+      </c>
+      <c r="I55">
+        <v>10</v>
+      </c>
+      <c r="J55">
+        <v>162.80000000000001</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="L55" t="b">
+        <v>1</v>
+      </c>
+      <c r="N55" t="s">
+        <v>668</v>
+      </c>
+      <c r="O55" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>240</v>
+      </c>
+      <c r="B56" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" t="s">
+        <v>239</v>
+      </c>
+      <c r="D56" t="s">
+        <v>238</v>
+      </c>
+      <c r="E56" t="s">
+        <v>146</v>
+      </c>
+      <c r="F56" t="s">
+        <v>145</v>
+      </c>
+      <c r="G56" t="b">
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
+        <v>604</v>
+      </c>
+      <c r="I56">
+        <v>4</v>
+      </c>
+      <c r="J56">
+        <v>31.8</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="L56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N56" s="7" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>237</v>
+      </c>
+      <c r="B57" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57" t="s">
+        <v>236</v>
+      </c>
+      <c r="D57" t="s">
+        <v>235</v>
+      </c>
+      <c r="E57" t="s">
+        <v>146</v>
+      </c>
+      <c r="F57" t="s">
+        <v>145</v>
+      </c>
+      <c r="G57" t="b">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
+        <v>607</v>
+      </c>
+      <c r="I57">
+        <v>5</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="L57" t="b">
+        <v>1</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>234</v>
+      </c>
+      <c r="B58" t="s">
+        <v>149</v>
+      </c>
+      <c r="C58" t="s">
+        <v>233</v>
+      </c>
+      <c r="D58" t="s">
+        <v>232</v>
+      </c>
+      <c r="E58" t="s">
+        <v>146</v>
+      </c>
+      <c r="F58" t="s">
+        <v>145</v>
+      </c>
+      <c r="G58" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>603</v>
+      </c>
+      <c r="I58">
+        <v>4</v>
+      </c>
+      <c r="J58">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="L58" t="b">
+        <v>1</v>
+      </c>
+      <c r="N58" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>231</v>
+      </c>
+      <c r="B59" t="s">
+        <v>149</v>
+      </c>
+      <c r="C59" t="s">
+        <v>230</v>
+      </c>
+      <c r="D59" t="s">
+        <v>229</v>
+      </c>
+      <c r="E59" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" t="s">
+        <v>145</v>
+      </c>
+      <c r="G59" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" t="s">
+        <v>606</v>
+      </c>
+      <c r="I59">
+        <v>5</v>
+      </c>
+      <c r="J59">
+        <v>3.9</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="L59" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>228</v>
+      </c>
+      <c r="B60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C60" t="s">
+        <v>227</v>
+      </c>
+      <c r="D60" t="s">
+        <v>226</v>
+      </c>
+      <c r="E60" t="s">
+        <v>146</v>
+      </c>
+      <c r="F60" t="s">
+        <v>145</v>
+      </c>
+      <c r="G60" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>621</v>
+      </c>
+      <c r="I60">
+        <v>9</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="s">
+        <v>720</v>
+      </c>
+      <c r="N60" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>225</v>
+      </c>
+      <c r="B61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" t="s">
+        <v>224</v>
+      </c>
+      <c r="D61" t="s">
+        <v>223</v>
+      </c>
+      <c r="E61" t="s">
+        <v>146</v>
+      </c>
+      <c r="F61" t="s">
+        <v>145</v>
+      </c>
+      <c r="G61" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" t="s">
+        <v>712</v>
+      </c>
+      <c r="I61">
+        <v>3</v>
+      </c>
+      <c r="J61">
+        <v>0.42</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="L61" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>222</v>
+      </c>
+      <c r="B62" t="s">
+        <v>149</v>
+      </c>
+      <c r="C62" t="s">
+        <v>221</v>
+      </c>
+      <c r="D62" t="s">
+        <v>220</v>
+      </c>
+      <c r="E62" t="s">
+        <v>146</v>
+      </c>
+      <c r="F62" t="s">
+        <v>145</v>
+      </c>
+      <c r="G62" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" t="s">
+        <v>618</v>
+      </c>
+      <c r="I62">
+        <v>8</v>
+      </c>
+      <c r="J62">
+        <v>13.2</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="L62" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62" t="s">
+        <v>715</v>
+      </c>
+      <c r="O62" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>219</v>
+      </c>
+      <c r="B63" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" t="s">
+        <v>218</v>
+      </c>
+      <c r="D63" t="s">
+        <v>217</v>
+      </c>
+      <c r="E63" t="s">
+        <v>146</v>
+      </c>
+      <c r="F63" t="s">
+        <v>145</v>
+      </c>
+      <c r="G63" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
+        <v>603</v>
+      </c>
+      <c r="I63">
+        <v>4</v>
+      </c>
+      <c r="J63">
+        <v>2.4</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="L63" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>216</v>
+      </c>
+      <c r="B64" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" t="s">
+        <v>215</v>
+      </c>
+      <c r="D64" t="s">
+        <v>214</v>
+      </c>
+      <c r="E64" t="s">
+        <v>146</v>
+      </c>
+      <c r="F64" t="s">
+        <v>145</v>
+      </c>
+      <c r="G64" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>612</v>
+      </c>
+      <c r="I64">
+        <v>10</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="L64" t="b">
+        <v>1</v>
+      </c>
+      <c r="N64" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>213</v>
+      </c>
+      <c r="B65" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" t="s">
+        <v>212</v>
+      </c>
+      <c r="D65" t="s">
+        <v>211</v>
+      </c>
+      <c r="E65" t="s">
+        <v>146</v>
+      </c>
+      <c r="F65" t="s">
+        <v>145</v>
+      </c>
+      <c r="G65" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>609</v>
+      </c>
+      <c r="I65">
+        <v>7</v>
+      </c>
+      <c r="J65">
+        <v>7.11</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="L65" t="b">
+        <v>1</v>
+      </c>
+      <c r="N65" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>210</v>
+      </c>
+      <c r="B66" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" t="s">
+        <v>209</v>
+      </c>
+      <c r="D66" t="s">
+        <v>208</v>
+      </c>
+      <c r="E66" t="s">
+        <v>146</v>
+      </c>
+      <c r="F66" t="s">
+        <v>145</v>
+      </c>
+      <c r="G66" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>608</v>
+      </c>
+      <c r="I66">
+        <v>6</v>
+      </c>
+      <c r="J66">
+        <v>5.4</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="L66" t="b">
+        <v>1</v>
+      </c>
+      <c r="N66" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>207</v>
+      </c>
+      <c r="B67" t="s">
+        <v>149</v>
+      </c>
+      <c r="C67" t="s">
+        <v>206</v>
+      </c>
+      <c r="D67" t="s">
+        <v>205</v>
+      </c>
+      <c r="E67" t="s">
+        <v>146</v>
+      </c>
+      <c r="F67" t="s">
+        <v>145</v>
+      </c>
+      <c r="G67" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
+        <v>611</v>
+      </c>
+      <c r="I67">
+        <v>9</v>
+      </c>
+      <c r="J67">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="L67" t="b">
+        <v>1</v>
+      </c>
+      <c r="N67" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>204</v>
+      </c>
+      <c r="B68" t="s">
+        <v>149</v>
+      </c>
+      <c r="C68" t="s">
+        <v>203</v>
+      </c>
+      <c r="D68" t="s">
+        <v>202</v>
+      </c>
+      <c r="E68" t="s">
+        <v>146</v>
+      </c>
+      <c r="F68" t="s">
+        <v>145</v>
+      </c>
+      <c r="G68" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" t="s">
+        <v>610</v>
+      </c>
+      <c r="I68">
+        <v>8</v>
+      </c>
+      <c r="J68">
+        <v>8.11</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="L68" t="b">
+        <v>1</v>
+      </c>
+      <c r="N68" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>201</v>
+      </c>
+      <c r="B69" t="s">
+        <v>149</v>
+      </c>
+      <c r="C69" t="s">
+        <v>200</v>
+      </c>
+      <c r="D69" t="s">
+        <v>199</v>
+      </c>
+      <c r="E69" t="s">
+        <v>146</v>
+      </c>
+      <c r="F69" t="s">
+        <v>145</v>
+      </c>
+      <c r="G69" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" t="s">
+        <v>606</v>
+      </c>
+      <c r="I69">
+        <v>5</v>
+      </c>
+      <c r="J69">
+        <v>3.9</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="L69" t="b">
+        <v>1</v>
+      </c>
+      <c r="N69" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>198</v>
+      </c>
+      <c r="B70" t="s">
+        <v>149</v>
+      </c>
+      <c r="C70" t="s">
+        <v>197</v>
+      </c>
+      <c r="D70" t="s">
+        <v>196</v>
+      </c>
+      <c r="E70" t="s">
+        <v>146</v>
+      </c>
+      <c r="F70" t="s">
+        <v>145</v>
+      </c>
+      <c r="G70" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
+        <v>621</v>
+      </c>
+      <c r="I70">
+        <v>9</v>
+      </c>
+      <c r="K70" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" t="s">
+        <v>720</v>
+      </c>
+      <c r="N70" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>195</v>
+      </c>
+      <c r="B71" t="s">
+        <v>149</v>
+      </c>
+      <c r="C71" t="s">
+        <v>194</v>
+      </c>
+      <c r="D71" t="s">
+        <v>193</v>
+      </c>
+      <c r="E71" t="s">
+        <v>146</v>
+      </c>
+      <c r="F71" t="s">
+        <v>145</v>
+      </c>
+      <c r="G71" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>712</v>
+      </c>
+      <c r="I71">
+        <v>3</v>
+      </c>
+      <c r="J71">
+        <v>0.73</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="L71" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" t="s">
+        <v>675</v>
+      </c>
+      <c r="N71" s="6" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>192</v>
+      </c>
+      <c r="B72" t="s">
+        <v>149</v>
+      </c>
+      <c r="C72" t="s">
+        <v>191</v>
+      </c>
+      <c r="D72" t="s">
+        <v>190</v>
+      </c>
+      <c r="E72" t="s">
+        <v>146</v>
+      </c>
+      <c r="F72" t="s">
+        <v>145</v>
+      </c>
+      <c r="G72" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>618</v>
+      </c>
+      <c r="I72">
+        <v>8</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="L72" t="b">
+        <v>1</v>
+      </c>
+      <c r="N72" t="s">
+        <v>715</v>
+      </c>
+      <c r="O72" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>189</v>
+      </c>
+      <c r="B73" t="s">
+        <v>149</v>
+      </c>
+      <c r="C73" t="s">
+        <v>188</v>
+      </c>
+      <c r="D73" t="s">
+        <v>187</v>
+      </c>
+      <c r="E73" t="s">
+        <v>146</v>
+      </c>
+      <c r="F73" t="s">
+        <v>145</v>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>604</v>
+      </c>
+      <c r="I73">
+        <v>4</v>
+      </c>
+      <c r="J73">
+        <v>31.8</v>
+      </c>
+      <c r="K73" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="L73" t="b">
+        <v>1</v>
+      </c>
+      <c r="N73" s="7" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>186</v>
+      </c>
+      <c r="B74" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" t="s">
+        <v>185</v>
+      </c>
+      <c r="D74" t="s">
+        <v>184</v>
+      </c>
+      <c r="E74" t="s">
+        <v>146</v>
+      </c>
+      <c r="F74" t="s">
+        <v>145</v>
+      </c>
+      <c r="G74" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" t="s">
+        <v>607</v>
+      </c>
+      <c r="I74">
+        <v>5</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="L74" t="b">
+        <v>1</v>
+      </c>
+      <c r="N74" s="7" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>183</v>
+      </c>
+      <c r="B75" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" t="s">
+        <v>182</v>
+      </c>
+      <c r="D75" t="s">
+        <v>181</v>
+      </c>
+      <c r="E75" t="s">
+        <v>146</v>
+      </c>
+      <c r="F75" t="s">
+        <v>145</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" t="s">
+        <v>621</v>
+      </c>
+      <c r="I75">
+        <v>9</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="L75" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75" t="s">
+        <v>720</v>
+      </c>
+      <c r="N75" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>180</v>
+      </c>
+      <c r="B76" t="s">
+        <v>149</v>
+      </c>
+      <c r="C76" t="s">
+        <v>179</v>
+      </c>
+      <c r="D76" t="s">
+        <v>178</v>
+      </c>
+      <c r="E76" t="s">
+        <v>146</v>
+      </c>
+      <c r="F76" t="s">
+        <v>145</v>
+      </c>
+      <c r="G76" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
+        <v>621</v>
+      </c>
+      <c r="I76">
+        <v>9</v>
+      </c>
+      <c r="K76" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="L76" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76" t="s">
+        <v>720</v>
+      </c>
+      <c r="N76" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>177</v>
+      </c>
+      <c r="B77" t="s">
+        <v>149</v>
+      </c>
+      <c r="C77" t="s">
+        <v>176</v>
+      </c>
+      <c r="D77" t="s">
+        <v>175</v>
+      </c>
+      <c r="E77" t="s">
+        <v>146</v>
+      </c>
+      <c r="F77" t="s">
+        <v>145</v>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" t="s">
+        <v>621</v>
+      </c>
+      <c r="I77">
+        <v>9</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" t="s">
+        <v>720</v>
+      </c>
+      <c r="N77" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>174</v>
+      </c>
+      <c r="B78" t="s">
+        <v>149</v>
+      </c>
+      <c r="C78" t="s">
+        <v>173</v>
+      </c>
+      <c r="D78" t="s">
+        <v>172</v>
+      </c>
+      <c r="E78" t="s">
+        <v>146</v>
+      </c>
+      <c r="F78" t="s">
+        <v>145</v>
+      </c>
+      <c r="G78" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" t="s">
+        <v>605</v>
+      </c>
+      <c r="I78">
+        <v>4</v>
+      </c>
+      <c r="J78">
+        <v>58.8</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="L78" t="b">
+        <v>1</v>
+      </c>
+      <c r="N78" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>171</v>
+      </c>
+      <c r="B79" t="s">
+        <v>149</v>
+      </c>
+      <c r="C79" t="s">
+        <v>170</v>
+      </c>
+      <c r="D79" t="s">
+        <v>169</v>
+      </c>
+      <c r="E79" t="s">
+        <v>146</v>
+      </c>
+      <c r="F79" t="s">
+        <v>145</v>
+      </c>
+      <c r="G79" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" t="s">
+        <v>604</v>
+      </c>
+      <c r="I79">
+        <v>4</v>
+      </c>
+      <c r="J79">
+        <v>31.8</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="L79" t="b">
+        <v>1</v>
+      </c>
+      <c r="N79" s="7" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>168</v>
+      </c>
+      <c r="B80" t="s">
+        <v>149</v>
+      </c>
+      <c r="C80" t="s">
+        <v>167</v>
+      </c>
+      <c r="D80" t="s">
+        <v>166</v>
+      </c>
+      <c r="E80" t="s">
+        <v>146</v>
+      </c>
+      <c r="F80" t="s">
+        <v>145</v>
+      </c>
+      <c r="G80" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" t="s">
+        <v>607</v>
+      </c>
+      <c r="I80">
+        <v>5</v>
+      </c>
+      <c r="K80" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="L80" t="b">
+        <v>1</v>
+      </c>
+      <c r="N80" s="7" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>165</v>
+      </c>
+      <c r="B81" t="s">
+        <v>149</v>
+      </c>
+      <c r="C81" t="s">
+        <v>164</v>
+      </c>
+      <c r="D81" t="s">
+        <v>163</v>
+      </c>
+      <c r="E81" t="s">
+        <v>146</v>
+      </c>
+      <c r="F81" t="s">
+        <v>145</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" t="s">
+        <v>610</v>
+      </c>
+      <c r="I81">
+        <v>8</v>
+      </c>
+      <c r="J81">
+        <v>5.4</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="L81" t="b">
+        <v>1</v>
+      </c>
+      <c r="N81" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" t="s">
+        <v>149</v>
+      </c>
+      <c r="C82" t="s">
+        <v>161</v>
+      </c>
+      <c r="D82" t="s">
+        <v>160</v>
+      </c>
+      <c r="E82" t="s">
+        <v>146</v>
+      </c>
+      <c r="F82" t="s">
+        <v>145</v>
+      </c>
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" t="s">
+        <v>608</v>
+      </c>
+      <c r="I82">
+        <v>6</v>
+      </c>
+      <c r="J82">
+        <v>5.95</v>
+      </c>
+      <c r="K82" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="L82" t="b">
+        <v>1</v>
+      </c>
+      <c r="N82" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>159</v>
+      </c>
+      <c r="B83" t="s">
+        <v>149</v>
+      </c>
+      <c r="C83" t="s">
+        <v>158</v>
+      </c>
+      <c r="D83" t="s">
+        <v>157</v>
+      </c>
+      <c r="E83" t="s">
+        <v>146</v>
+      </c>
+      <c r="F83" t="s">
+        <v>145</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" t="s">
+        <v>621</v>
+      </c>
+      <c r="I83">
+        <v>9</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="L83" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" t="s">
+        <v>720</v>
+      </c>
+      <c r="N83" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>156</v>
+      </c>
+      <c r="B84" t="s">
+        <v>149</v>
+      </c>
+      <c r="C84" t="s">
+        <v>155</v>
+      </c>
+      <c r="D84" t="s">
+        <v>154</v>
+      </c>
+      <c r="E84" t="s">
+        <v>146</v>
+      </c>
+      <c r="F84" t="s">
+        <v>145</v>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" t="s">
+        <v>608</v>
+      </c>
+      <c r="I84">
+        <v>6</v>
+      </c>
+      <c r="K84" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="L84" t="b">
+        <v>1</v>
+      </c>
+      <c r="N84" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>153</v>
+      </c>
+      <c r="B85" t="s">
+        <v>149</v>
+      </c>
+      <c r="C85" t="s">
+        <v>152</v>
+      </c>
+      <c r="D85" t="s">
+        <v>151</v>
+      </c>
+      <c r="E85" t="s">
+        <v>146</v>
+      </c>
+      <c r="F85" t="s">
+        <v>145</v>
+      </c>
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
+        <v>608</v>
+      </c>
+      <c r="I85">
+        <v>6</v>
+      </c>
+      <c r="J85">
+        <v>5.45</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="L85" t="b">
+        <v>1</v>
+      </c>
+      <c r="N85" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>150</v>
+      </c>
+      <c r="B86" t="s">
+        <v>149</v>
+      </c>
+      <c r="C86" t="s">
+        <v>148</v>
+      </c>
+      <c r="D86" t="s">
+        <v>147</v>
+      </c>
+      <c r="E86" t="s">
+        <v>146</v>
+      </c>
+      <c r="F86" t="s">
+        <v>145</v>
+      </c>
+      <c r="G86" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" t="s">
+        <v>621</v>
+      </c>
+      <c r="I86">
+        <v>9</v>
+      </c>
+      <c r="K86" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="L86" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" t="s">
+        <v>720</v>
+      </c>
+      <c r="N86" t="s">
+        <v>715</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D266DCE-4082-48D6-BEDB-61E5E2666536}">
   <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -6490,7 +11058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D208FD11-3A3C-4357-9FF7-ED2CAF88E4C2}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>

--- a/Mechanism_info/measurement_info.xlsx
+++ b/Mechanism_info/measurement_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u1545774\Documents\GitHub\USOS_shared\Mechanism_info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01153EE7-C0CA-4AB6-A89A-8E3F3A0997E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B067085B-C89B-4E77-8DE7-970CA2C86D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11685" yWindow="2813" windowWidth="17145" windowHeight="11835" activeTab="1" xr2:uid="{698A9B32-3AC5-4EFA-9C0D-28F7A7FA4C52}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{698A9B32-3AC5-4EFA-9C0D-28F7A7FA4C52}"/>
   </bookViews>
   <sheets>
     <sheet name="Mobile_Lab_Measurements" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="744">
   <si>
     <t>Portable Optical Particle Spectrometer (POPS)</t>
   </si>
@@ -1437,9 +1437,6 @@
     <t>C10H17NO4_CIMS</t>
   </si>
   <si>
-    <t>Total concentration of C5 organic nitrates with formula C5H0NO5 in ambient air</t>
-  </si>
-  <si>
     <t>C5H9NO5_CIMS</t>
   </si>
   <si>
@@ -2248,6 +2245,33 @@
   </si>
   <si>
     <t>Other Alkenes</t>
+  </si>
+  <si>
+    <t>GEOS-Chem Notes</t>
+  </si>
+  <si>
+    <t>ICN + INPB+INPD+ITCN+IDN+ITHN+IHN1+IHN2+IHN3+IHN4</t>
+  </si>
+  <si>
+    <t>INPB+INPD</t>
+  </si>
+  <si>
+    <t>MCRHNB+MCRHN+MVKN</t>
+  </si>
+  <si>
+    <t>SOA precursor; isoprene oxidation products</t>
+  </si>
+  <si>
+    <t>IEPOXA+IEPOXD+IEPOXB+RIPA+RIPB+RIPC+RIPD</t>
+  </si>
+  <si>
+    <t>APINN+BPINN+LIMN+PIN+LIMPAN+PINPAN+MONITU+MONITS</t>
+  </si>
+  <si>
+    <t>STYRE+XYLE+EBZ+TMB</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -2280,7 +2304,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2290,6 +2314,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2341,7 +2371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2364,6 +2394,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2678,61 +2709,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451096C0-28AF-4EBA-9A8D-CDAC8E348A85}">
-  <dimension ref="A1:J191"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:L191"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.3984375" customWidth="1"/>
-    <col min="3" max="4" width="13.19921875" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="3" max="4" width="13.140625" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="11" max="11" width="33.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>627</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K1" s="3" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B2" t="s">
         <v>149</v>
       </c>
       <c r="C2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F2" t="s">
         <v>380</v>
@@ -2741,21 +2776,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B3" t="s">
         <v>149</v>
       </c>
       <c r="C3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F3" t="s">
         <v>380</v>
@@ -2764,21 +2799,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B4" t="s">
         <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F4" t="s">
         <v>380</v>
@@ -2787,21 +2822,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B5" t="s">
         <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F5" t="s">
         <v>380</v>
@@ -2810,21 +2845,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B6" t="s">
         <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F6" t="s">
         <v>380</v>
@@ -2833,21 +2868,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B7" t="s">
         <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F7" t="s">
         <v>380</v>
@@ -2856,152 +2891,152 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B8" t="s">
         <v>138</v>
       </c>
       <c r="D8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B9" t="s">
         <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E9" t="s">
+        <v>476</v>
+      </c>
+      <c r="F9" t="s">
+        <v>483</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>488</v>
+      </c>
+      <c r="B10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" t="s">
+        <v>487</v>
+      </c>
+      <c r="D10" t="s">
+        <v>486</v>
+      </c>
+      <c r="E10" t="s">
+        <v>476</v>
+      </c>
+      <c r="F10" t="s">
+        <v>483</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>485</v>
+      </c>
+      <c r="B11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" t="s">
+        <v>484</v>
+      </c>
+      <c r="E11" t="s">
+        <v>476</v>
+      </c>
+      <c r="F11" t="s">
+        <v>483</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>482</v>
+      </c>
+      <c r="B12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" t="s">
+        <v>481</v>
+      </c>
+      <c r="E12" t="s">
+        <v>476</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>480</v>
+      </c>
+      <c r="B13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" t="s">
+        <v>479</v>
+      </c>
+      <c r="E13" t="s">
+        <v>476</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>478</v>
+      </c>
+      <c r="B14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" t="s">
         <v>477</v>
       </c>
-      <c r="F9" t="s">
-        <v>484</v>
-      </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>489</v>
-      </c>
-      <c r="B10" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" t="s">
-        <v>488</v>
-      </c>
-      <c r="D10" t="s">
-        <v>487</v>
-      </c>
-      <c r="E10" t="s">
-        <v>477</v>
-      </c>
-      <c r="F10" t="s">
-        <v>484</v>
-      </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>486</v>
-      </c>
-      <c r="B11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D11" t="s">
-        <v>485</v>
-      </c>
-      <c r="E11" t="s">
-        <v>477</v>
-      </c>
-      <c r="F11" t="s">
-        <v>484</v>
-      </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>483</v>
-      </c>
-      <c r="B12" t="s">
-        <v>149</v>
-      </c>
-      <c r="D12" t="s">
-        <v>482</v>
-      </c>
-      <c r="E12" t="s">
-        <v>477</v>
-      </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>481</v>
-      </c>
-      <c r="B13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D13" t="s">
-        <v>480</v>
-      </c>
-      <c r="E13" t="s">
-        <v>477</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>479</v>
-      </c>
-      <c r="B14" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" t="s">
-        <v>478</v>
-      </c>
       <c r="E14" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B15" t="s">
         <v>149</v>
       </c>
       <c r="C15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F15" t="s">
         <v>380</v>
@@ -3010,107 +3045,125 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>472</v>
-      </c>
-      <c r="B16" t="s">
-        <v>149</v>
-      </c>
-      <c r="D16" t="s">
+    <row r="16" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="E16" t="s">
+      <c r="B16" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>470</v>
-      </c>
-      <c r="B17" t="s">
-        <v>149</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="G16" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="E17" t="s">
+      <c r="B17" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>468</v>
-      </c>
-      <c r="B18" t="s">
-        <v>149</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="G17" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="E18" t="s">
+      <c r="B18" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>466</v>
-      </c>
-      <c r="B19" t="s">
-        <v>149</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="G18" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="E19" t="s">
+      <c r="B19" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>724</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
+      <c r="G19" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="B20" t="s">
-        <v>149</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="B20" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="G20" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>461</v>
       </c>
@@ -3133,7 +3186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>457</v>
       </c>
@@ -3159,7 +3212,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>454</v>
       </c>
@@ -3185,7 +3238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>451</v>
       </c>
@@ -3211,7 +3264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>448</v>
       </c>
@@ -3237,30 +3290,30 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
+    <row r="26" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="B26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B26" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="G26" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>442</v>
       </c>
@@ -3286,30 +3339,30 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
+    <row r="28" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="B28" t="s">
-        <v>149</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="B28" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28">
+      <c r="G28" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" s="10">
         <v>0.2</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>438</v>
       </c>
@@ -3335,7 +3388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>435</v>
       </c>
@@ -3361,7 +3414,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>433</v>
       </c>
@@ -3384,7 +3437,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>431</v>
       </c>
@@ -3410,7 +3463,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>429</v>
       </c>
@@ -3436,7 +3489,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>427</v>
       </c>
@@ -3459,7 +3512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>424</v>
       </c>
@@ -3485,73 +3538,79 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
+    <row r="36" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="B36" t="s">
-        <v>149</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="B36" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="G36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
+      <c r="G36" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="B37" t="s">
-        <v>149</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="B37" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="G37" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37">
+      <c r="G37" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" s="10">
         <v>22</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
+      <c r="K37" s="10" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="B38" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B38" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="G38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="G38" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>414</v>
       </c>
@@ -3574,7 +3633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>411</v>
       </c>
@@ -3594,7 +3653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>409</v>
       </c>
@@ -3617,53 +3676,53 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
+    <row r="42" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="B42" t="s">
-        <v>149</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B42" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="G42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
+      <c r="G42" s="10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="B43" t="s">
-        <v>149</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B43" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="G43" s="10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>398</v>
       </c>
@@ -3686,30 +3745,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
+    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="B45" t="s">
-        <v>149</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B45" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="G45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="G45" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>392</v>
       </c>
@@ -3732,7 +3791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>388</v>
       </c>
@@ -3758,7 +3817,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>384</v>
       </c>
@@ -3781,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>379</v>
       </c>
@@ -3804,7 +3863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>374</v>
       </c>
@@ -3824,7 +3883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>371</v>
       </c>
@@ -3844,7 +3903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>369</v>
       </c>
@@ -3864,7 +3923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>367</v>
       </c>
@@ -3884,7 +3943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>365</v>
       </c>
@@ -3904,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>362</v>
       </c>
@@ -3924,7 +3983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>358</v>
       </c>
@@ -3944,7 +4003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>356</v>
       </c>
@@ -3964,7 +4023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>354</v>
       </c>
@@ -3984,7 +4043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>351</v>
       </c>
@@ -4004,7 +4063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>347</v>
       </c>
@@ -4024,7 +4083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>345</v>
       </c>
@@ -4047,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>342</v>
       </c>
@@ -4070,7 +4129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>340</v>
       </c>
@@ -4093,7 +4152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>337</v>
       </c>
@@ -4116,7 +4175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>333</v>
       </c>
@@ -4142,7 +4201,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>330</v>
       </c>
@@ -4165,7 +4224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>327</v>
       </c>
@@ -4188,7 +4247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>322</v>
       </c>
@@ -4208,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>321</v>
       </c>
@@ -4228,7 +4287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>320</v>
       </c>
@@ -4248,7 +4307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>318</v>
       </c>
@@ -4274,7 +4333,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>315</v>
       </c>
@@ -4300,7 +4359,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>312</v>
       </c>
@@ -4326,7 +4385,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>309</v>
       </c>
@@ -4349,7 +4408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>306</v>
       </c>
@@ -4372,7 +4431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>303</v>
       </c>
@@ -4395,7 +4454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>300</v>
       </c>
@@ -4418,7 +4477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>297</v>
       </c>
@@ -4441,7 +4500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>294</v>
       </c>
@@ -4464,7 +4523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>291</v>
       </c>
@@ -4487,7 +4546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>288</v>
       </c>
@@ -4510,7 +4569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>285</v>
       </c>
@@ -4536,7 +4595,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>282</v>
       </c>
@@ -4562,7 +4621,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>279</v>
       </c>
@@ -4588,7 +4647,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>276</v>
       </c>
@@ -4614,7 +4673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>273</v>
       </c>
@@ -4640,7 +4699,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>270</v>
       </c>
@@ -4666,7 +4725,7 @@
         <v>162.80000000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>267</v>
       </c>
@@ -4689,7 +4748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>264</v>
       </c>
@@ -4712,7 +4771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>261</v>
       </c>
@@ -4738,7 +4797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>258</v>
       </c>
@@ -4761,7 +4820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>255</v>
       </c>
@@ -4787,7 +4846,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>252</v>
       </c>
@@ -4813,7 +4872,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>249</v>
       </c>
@@ -4839,7 +4898,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>246</v>
       </c>
@@ -4865,7 +4924,7 @@
         <v>162.80000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>243</v>
       </c>
@@ -4891,7 +4950,7 @@
         <v>162.80000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>240</v>
       </c>
@@ -4917,7 +4976,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>237</v>
       </c>
@@ -4940,7 +4999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>234</v>
       </c>
@@ -4966,7 +5025,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>231</v>
       </c>
@@ -4992,56 +5051,56 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A101" t="s">
+    <row r="101" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="B101" t="s">
-        <v>149</v>
-      </c>
-      <c r="C101" t="s">
+      <c r="B101" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C101" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E101" t="s">
-        <v>146</v>
-      </c>
-      <c r="F101" t="s">
-        <v>145</v>
-      </c>
-      <c r="G101" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A102" t="s">
+      <c r="E101" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G101" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B102" t="s">
-        <v>149</v>
-      </c>
-      <c r="C102" t="s">
+      <c r="B102" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C102" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="E102" t="s">
-        <v>146</v>
-      </c>
-      <c r="F102" t="s">
-        <v>145</v>
-      </c>
-      <c r="G102" t="b">
-        <v>1</v>
-      </c>
-      <c r="J102">
+      <c r="E102" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="G102" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J102" s="10">
         <v>0.42</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>222</v>
       </c>
@@ -5067,7 +5126,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>219</v>
       </c>
@@ -5093,7 +5152,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>216</v>
       </c>
@@ -5116,7 +5175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>213</v>
       </c>
@@ -5142,7 +5201,7 @@
         <v>7.11</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>210</v>
       </c>
@@ -5168,7 +5227,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>207</v>
       </c>
@@ -5194,7 +5253,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>204</v>
       </c>
@@ -5220,7 +5279,7 @@
         <v>8.11</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>201</v>
       </c>
@@ -5246,7 +5305,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>198</v>
       </c>
@@ -5269,33 +5328,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A112" t="s">
+    <row r="112" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="B112" t="s">
-        <v>149</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="B112" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C112" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E112" t="s">
-        <v>146</v>
-      </c>
-      <c r="F112" t="s">
-        <v>145</v>
-      </c>
-      <c r="G112" t="b">
-        <v>1</v>
-      </c>
-      <c r="J112">
+      <c r="E112" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F112" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="G112" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J112" s="10">
         <v>0.73</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>192</v>
       </c>
@@ -5318,7 +5377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>189</v>
       </c>
@@ -5344,7 +5403,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>186</v>
       </c>
@@ -5367,7 +5426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>183</v>
       </c>
@@ -5390,7 +5449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>180</v>
       </c>
@@ -5413,7 +5472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>177</v>
       </c>
@@ -5436,7 +5495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>174</v>
       </c>
@@ -5462,7 +5521,7 @@
         <v>58.8</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>171</v>
       </c>
@@ -5488,7 +5547,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>168</v>
       </c>
@@ -5511,7 +5570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>165</v>
       </c>
@@ -5537,7 +5596,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>162</v>
       </c>
@@ -5563,7 +5622,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>159</v>
       </c>
@@ -5586,7 +5645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>156</v>
       </c>
@@ -5609,7 +5668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>153</v>
       </c>
@@ -5635,7 +5694,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>150</v>
       </c>
@@ -5658,7 +5717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>144</v>
       </c>
@@ -5678,7 +5737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -5698,7 +5757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>101</v>
       </c>
@@ -5718,7 +5777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>134</v>
       </c>
@@ -5738,7 +5797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>132</v>
       </c>
@@ -5758,7 +5817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>130</v>
       </c>
@@ -5778,7 +5837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>128</v>
       </c>
@@ -5798,7 +5857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>126</v>
       </c>
@@ -5818,7 +5877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>124</v>
       </c>
@@ -5838,7 +5897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>122</v>
       </c>
@@ -5858,7 +5917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>120</v>
       </c>
@@ -5878,7 +5937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>118</v>
       </c>
@@ -5898,7 +5957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>116</v>
       </c>
@@ -5918,7 +5977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>114</v>
       </c>
@@ -5938,7 +5997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>112</v>
       </c>
@@ -5958,7 +6017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>110</v>
       </c>
@@ -5978,7 +6037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>108</v>
       </c>
@@ -5998,7 +6057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>106</v>
       </c>
@@ -6018,7 +6077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>104</v>
       </c>
@@ -6038,7 +6097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>99</v>
       </c>
@@ -6058,7 +6117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>97</v>
       </c>
@@ -6078,7 +6137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>94</v>
       </c>
@@ -6098,7 +6157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>91</v>
       </c>
@@ -6118,7 +6177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>88</v>
       </c>
@@ -6138,7 +6197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>86</v>
       </c>
@@ -6158,7 +6217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>83</v>
       </c>
@@ -6178,7 +6237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>80</v>
       </c>
@@ -6198,7 +6257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>77</v>
       </c>
@@ -6218,7 +6277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>74</v>
       </c>
@@ -6238,7 +6297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>72</v>
       </c>
@@ -6258,7 +6317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>70</v>
       </c>
@@ -6278,7 +6337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>68</v>
       </c>
@@ -6298,7 +6357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>66</v>
       </c>
@@ -6318,7 +6377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>64</v>
       </c>
@@ -6338,7 +6397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>62</v>
       </c>
@@ -6358,7 +6417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>60</v>
       </c>
@@ -6378,7 +6437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>58</v>
       </c>
@@ -6398,7 +6457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>56</v>
       </c>
@@ -6418,7 +6477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>54</v>
       </c>
@@ -6438,7 +6497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>52</v>
       </c>
@@ -6458,7 +6517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>50</v>
       </c>
@@ -6478,7 +6537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>48</v>
       </c>
@@ -6498,7 +6557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>46</v>
       </c>
@@ -6518,7 +6577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>44</v>
       </c>
@@ -6538,7 +6597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>42</v>
       </c>
@@ -6558,7 +6617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>40</v>
       </c>
@@ -6578,7 +6637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>38</v>
       </c>
@@ -6598,7 +6657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>36</v>
       </c>
@@ -6618,7 +6677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>34</v>
       </c>
@@ -6638,7 +6697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>32</v>
       </c>
@@ -6658,7 +6717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>30</v>
       </c>
@@ -6678,7 +6737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>28</v>
       </c>
@@ -6698,7 +6757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>26</v>
       </c>
@@ -6718,7 +6777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>24</v>
       </c>
@@ -6738,7 +6797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>22</v>
       </c>
@@ -6758,7 +6817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>20</v>
       </c>
@@ -6778,7 +6837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -6798,7 +6857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>16</v>
       </c>
@@ -6818,7 +6877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>14</v>
       </c>
@@ -6838,7 +6897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>12</v>
       </c>
@@ -6858,7 +6917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>10</v>
       </c>
@@ -6878,7 +6937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>8</v>
       </c>
@@ -6898,7 +6957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>6</v>
       </c>
@@ -6918,7 +6977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>4</v>
       </c>
@@ -6946,72 +7005,74 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C25CDB93-1C32-4E52-9A4C-B188A4943EDD}">
   <dimension ref="A1:O86"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.3984375" customWidth="1"/>
-    <col min="3" max="3" width="13.19921875" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="59.42578125" customWidth="1"/>
     <col min="5" max="5" width="25" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="34.265625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" customWidth="1"/>
+    <col min="7" max="7" width="42.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" customWidth="1"/>
+    <col min="11" max="11" width="34.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="K1" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>628</v>
-      </c>
       <c r="L1" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>674</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>673</v>
-      </c>
       <c r="O1" s="9" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B2" t="s">
         <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E2" t="s">
         <v>462</v>
@@ -7023,21 +7084,21 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B3" t="s">
         <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E3" t="s">
         <v>462</v>
@@ -7052,18 +7113,18 @@
         <v>5</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B4" t="s">
         <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E4" t="s">
         <v>462</v>
@@ -7075,21 +7136,21 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="I4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B5" t="s">
         <v>149</v>
       </c>
       <c r="D5" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E5" t="s">
         <v>462</v>
@@ -7101,16 +7162,16 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>464</v>
       </c>
@@ -7130,16 +7191,16 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>457</v>
       </c>
@@ -7162,7 +7223,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -7171,16 +7232,16 @@
         <v>0.8</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>454</v>
       </c>
@@ -7203,7 +7264,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -7212,16 +7273,16 @@
         <v>0</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>451</v>
       </c>
@@ -7244,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -7253,16 +7314,16 @@
         <v>15</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>448</v>
       </c>
@@ -7285,7 +7346,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -7294,16 +7355,16 @@
         <v>3.2</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>445</v>
       </c>
@@ -7326,22 +7387,22 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>442</v>
       </c>
@@ -7364,7 +7425,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="I12">
         <v>3</v>
@@ -7373,16 +7434,16 @@
         <v>20</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>440</v>
       </c>
@@ -7402,7 +7463,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="I13">
         <v>3</v>
@@ -7411,19 +7472,19 @@
         <v>0.2</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>438</v>
       </c>
@@ -7446,7 +7507,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -7455,16 +7516,16 @@
         <v>6</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>435</v>
       </c>
@@ -7487,7 +7548,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="I15">
         <v>5</v>
@@ -7496,22 +7557,22 @@
         <v>100</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N15" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O15" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>433</v>
       </c>
@@ -7537,16 +7598,16 @@
         <v>24.8</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>431</v>
       </c>
@@ -7569,7 +7630,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I17">
         <v>6</v>
@@ -7578,19 +7639,19 @@
         <v>1.2</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="O17" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>429</v>
       </c>
@@ -7613,7 +7674,7 @@
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -7622,19 +7683,19 @@
         <v>5.6</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="O18" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>427</v>
       </c>
@@ -7657,25 +7718,25 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I19">
         <v>8</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="N19" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>424</v>
       </c>
@@ -7698,7 +7759,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -7707,19 +7768,19 @@
         <v>12</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="N20" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>421</v>
       </c>
@@ -7739,25 +7800,25 @@
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="I21">
         <v>8</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N21" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>419</v>
       </c>
@@ -7777,7 +7838,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I22">
         <v>9</v>
@@ -7786,16 +7847,16 @@
         <v>22</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>417</v>
       </c>
@@ -7818,25 +7879,25 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="N23" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>414</v>
       </c>
@@ -7859,22 +7920,22 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="I24">
         <v>8</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>411</v>
       </c>
@@ -7894,22 +7955,22 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I25">
         <v>10</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>409</v>
       </c>
@@ -7932,22 +7993,22 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="I26">
         <v>9</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>403</v>
       </c>
@@ -7970,22 +8031,22 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="I27">
         <v>10</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>388</v>
       </c>
@@ -8008,7 +8069,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="I28">
         <v>1</v>
@@ -8017,16 +8078,16 @@
         <v>0.4</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>333</v>
       </c>
@@ -8049,7 +8110,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I29">
         <v>1</v>
@@ -8058,16 +8119,16 @@
         <v>8.5</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>318</v>
       </c>
@@ -8090,7 +8151,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="I30">
         <v>3</v>
@@ -8099,16 +8160,16 @@
         <v>0.2</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="L30" t="b">
         <v>1</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>315</v>
       </c>
@@ -8131,7 +8192,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="I31">
         <v>3</v>
@@ -8140,19 +8201,19 @@
         <v>20</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N31" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>312</v>
       </c>
@@ -8175,7 +8236,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -8184,22 +8245,22 @@
         <v>1.2</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N32" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="O32" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>309</v>
       </c>
@@ -8222,22 +8283,22 @@
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="I33">
         <v>2</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="L33" t="b">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>306</v>
       </c>
@@ -8260,22 +8321,22 @@
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I34">
         <v>2</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>303</v>
       </c>
@@ -8298,22 +8359,22 @@
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="I35">
         <v>2</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>300</v>
       </c>
@@ -8336,22 +8397,22 @@
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="I36">
         <v>1</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>297</v>
       </c>
@@ -8374,22 +8435,22 @@
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="I37">
         <v>1</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>294</v>
       </c>
@@ -8412,25 +8473,25 @@
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="I38">
         <v>1</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="L38" t="b">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="O38" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>291</v>
       </c>
@@ -8453,22 +8514,22 @@
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="I39">
         <v>1</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="L39" t="b">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>288</v>
       </c>
@@ -8491,22 +8552,22 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I40">
         <v>5</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L40" t="b">
         <v>1</v>
       </c>
       <c r="N40" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.45">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>285</v>
       </c>
@@ -8529,7 +8590,7 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="I41">
         <v>8</v>
@@ -8538,16 +8599,16 @@
         <v>13.2</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L41" t="b">
         <v>1</v>
       </c>
       <c r="N41" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>282</v>
       </c>
@@ -8570,7 +8631,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I42">
         <v>2</v>
@@ -8579,16 +8640,16 @@
         <v>0.24</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L42" t="b">
         <v>1</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.45">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>279</v>
       </c>
@@ -8611,7 +8672,7 @@
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="I43">
         <v>2</v>
@@ -8620,16 +8681,16 @@
         <v>7.8</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
       </c>
       <c r="N43" s="7" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.45">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>276</v>
       </c>
@@ -8652,7 +8713,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="I44">
         <v>2</v>
@@ -8661,16 +8722,16 @@
         <v>1</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L44" t="b">
         <v>1</v>
       </c>
       <c r="N44" s="7" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.45">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>273</v>
       </c>
@@ -8693,7 +8754,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="I45">
         <v>4</v>
@@ -8702,16 +8763,16 @@
         <v>40</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.45">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>270</v>
       </c>
@@ -8734,7 +8795,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="I46">
         <v>5</v>
@@ -8743,19 +8804,19 @@
         <v>162.80000000000001</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L46" t="b">
         <v>1</v>
       </c>
       <c r="N46" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O46" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.45">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>267</v>
       </c>
@@ -8781,19 +8842,19 @@
         <v>19</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O47" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>264</v>
       </c>
@@ -8816,25 +8877,25 @@
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I48">
         <v>4</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
       </c>
       <c r="M48" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="N48" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>261</v>
       </c>
@@ -8857,7 +8918,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="I49">
         <v>7</v>
@@ -8866,16 +8927,16 @@
         <v>11</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L49" t="b">
         <v>1</v>
       </c>
       <c r="N49" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>258</v>
       </c>
@@ -8898,22 +8959,22 @@
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="I50">
         <v>6</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
       </c>
       <c r="N50" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>255</v>
       </c>
@@ -8936,7 +8997,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="I51">
         <v>3</v>
@@ -8945,16 +9006,16 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
       </c>
       <c r="N51" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>252</v>
       </c>
@@ -8977,7 +9038,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="I52">
         <v>3</v>
@@ -8986,16 +9047,16 @@
         <v>30</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L52" t="b">
         <v>1</v>
       </c>
       <c r="N52" s="7" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>249</v>
       </c>
@@ -9018,7 +9079,7 @@
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I53">
         <v>7</v>
@@ -9027,19 +9088,19 @@
         <v>5.6</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
       </c>
       <c r="M53" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N53" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>246</v>
       </c>
@@ -9062,7 +9123,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I54">
         <v>10</v>
@@ -9071,19 +9132,19 @@
         <v>162.80000000000001</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="L54" t="b">
         <v>1</v>
       </c>
       <c r="N54" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O54" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>243</v>
       </c>
@@ -9106,7 +9167,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I55">
         <v>10</v>
@@ -9115,19 +9176,19 @@
         <v>162.80000000000001</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L55" t="b">
         <v>1</v>
       </c>
       <c r="N55" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O55" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>240</v>
       </c>
@@ -9150,7 +9211,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I56">
         <v>4</v>
@@ -9159,16 +9220,16 @@
         <v>31.8</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
       </c>
       <c r="N56" s="7" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.45">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>237</v>
       </c>
@@ -9191,22 +9252,22 @@
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I57">
         <v>5</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L57" t="b">
         <v>1</v>
       </c>
       <c r="N57" s="7" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.45">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>234</v>
       </c>
@@ -9229,7 +9290,7 @@
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I58">
         <v>4</v>
@@ -9238,16 +9299,16 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
       </c>
       <c r="N58" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>231</v>
       </c>
@@ -9270,7 +9331,7 @@
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I59">
         <v>5</v>
@@ -9279,16 +9340,16 @@
         <v>3.9</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L59" t="b">
         <v>1</v>
       </c>
       <c r="N59" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>228</v>
       </c>
@@ -9311,25 +9372,25 @@
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I60">
         <v>9</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N60" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>225</v>
       </c>
@@ -9352,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I61">
         <v>3</v>
@@ -9361,16 +9422,16 @@
         <v>0.42</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>222</v>
       </c>
@@ -9393,7 +9454,7 @@
         <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="I62">
         <v>8</v>
@@ -9402,19 +9463,19 @@
         <v>13.2</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="L62" t="b">
         <v>1</v>
       </c>
       <c r="N62" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="O62" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.45">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>219</v>
       </c>
@@ -9437,7 +9498,7 @@
         <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I63">
         <v>4</v>
@@ -9446,16 +9507,16 @@
         <v>2.4</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
       </c>
       <c r="N63" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>216</v>
       </c>
@@ -9478,22 +9539,22 @@
         <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="I64">
         <v>10</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
       </c>
       <c r="N64" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>213</v>
       </c>
@@ -9516,7 +9577,7 @@
         <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I65">
         <v>7</v>
@@ -9525,16 +9586,16 @@
         <v>7.11</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
       </c>
       <c r="N65" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>210</v>
       </c>
@@ -9557,7 +9618,7 @@
         <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I66">
         <v>6</v>
@@ -9566,16 +9627,16 @@
         <v>5.4</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L66" t="b">
         <v>1</v>
       </c>
       <c r="N66" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>207</v>
       </c>
@@ -9598,7 +9659,7 @@
         <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="I67">
         <v>9</v>
@@ -9607,16 +9668,16 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="L67" t="b">
         <v>1</v>
       </c>
       <c r="N67" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>204</v>
       </c>
@@ -9639,7 +9700,7 @@
         <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I68">
         <v>8</v>
@@ -9648,16 +9709,16 @@
         <v>8.11</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="L68" t="b">
         <v>1</v>
       </c>
       <c r="N68" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>201</v>
       </c>
@@ -9680,7 +9741,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I69">
         <v>5</v>
@@ -9689,16 +9750,16 @@
         <v>3.9</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
       </c>
       <c r="N69" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>198</v>
       </c>
@@ -9721,25 +9782,25 @@
         <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I70">
         <v>9</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
       </c>
       <c r="M70" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N70" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>195</v>
       </c>
@@ -9762,7 +9823,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I71">
         <v>3</v>
@@ -9771,19 +9832,19 @@
         <v>0.73</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
       </c>
       <c r="M71" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>192</v>
       </c>
@@ -9806,25 +9867,25 @@
         <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="I72">
         <v>8</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
       </c>
       <c r="N72" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="O72" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>189</v>
       </c>
@@ -9847,7 +9908,7 @@
         <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I73">
         <v>4</v>
@@ -9856,16 +9917,16 @@
         <v>31.8</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
       </c>
       <c r="N73" s="7" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>186</v>
       </c>
@@ -9888,22 +9949,22 @@
         <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I74">
         <v>5</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L74" t="b">
         <v>1</v>
       </c>
       <c r="N74" s="7" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>183</v>
       </c>
@@ -9926,25 +9987,25 @@
         <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I75">
         <v>9</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
       </c>
       <c r="M75" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N75" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>180</v>
       </c>
@@ -9967,25 +10028,25 @@
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I76">
         <v>9</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
       </c>
       <c r="M76" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N76" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>177</v>
       </c>
@@ -10008,25 +10069,25 @@
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I77">
         <v>9</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
       </c>
       <c r="M77" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N77" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>174</v>
       </c>
@@ -10049,7 +10110,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I78">
         <v>4</v>
@@ -10058,16 +10119,16 @@
         <v>58.8</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
       </c>
       <c r="N78" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>171</v>
       </c>
@@ -10090,7 +10151,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I79">
         <v>4</v>
@@ -10099,16 +10160,16 @@
         <v>31.8</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="L79" t="b">
         <v>1</v>
       </c>
       <c r="N79" s="7" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>168</v>
       </c>
@@ -10131,22 +10192,22 @@
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I80">
         <v>5</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
       </c>
       <c r="N80" s="7" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>165</v>
       </c>
@@ -10169,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I81">
         <v>8</v>
@@ -10178,16 +10239,16 @@
         <v>5.4</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
       </c>
       <c r="N81" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>162</v>
       </c>
@@ -10210,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I82">
         <v>6</v>
@@ -10219,16 +10280,16 @@
         <v>5.95</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L82" t="b">
         <v>1</v>
       </c>
       <c r="N82" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>159</v>
       </c>
@@ -10251,25 +10312,25 @@
         <v>1</v>
       </c>
       <c r="H83" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I83">
         <v>9</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
       </c>
       <c r="M83" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N83" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>156</v>
       </c>
@@ -10292,22 +10353,22 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I84">
         <v>6</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L84" t="b">
         <v>1</v>
       </c>
       <c r="N84" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>153</v>
       </c>
@@ -10330,7 +10391,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I85">
         <v>6</v>
@@ -10339,16 +10400,16 @@
         <v>5.45</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L85" t="b">
         <v>1</v>
       </c>
       <c r="N85" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>150</v>
       </c>
@@ -10371,22 +10432,22 @@
         <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I86">
         <v>9</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
       </c>
       <c r="M86" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N86" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -10398,656 +10459,656 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D266DCE-4082-48D6-BEDB-61E5E2666536}">
   <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.06640625" customWidth="1"/>
-    <col min="2" max="2" width="17.19921875" customWidth="1"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B1" t="s">
+        <v>595</v>
+      </c>
+      <c r="D1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D2" t="s">
         <v>578</v>
       </c>
-      <c r="B1" t="s">
-        <v>596</v>
-      </c>
-      <c r="D1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>520</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>597</v>
-      </c>
-      <c r="D2" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>521</v>
-      </c>
-      <c r="B3" t="s">
-        <v>598</v>
       </c>
       <c r="D3" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D4" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D5" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D6" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D7" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D8" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D9" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D10" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D11" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B12" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D12" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B13" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D13" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D14" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D15" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B16" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D16" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B17" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D17" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B18" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D18" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D19" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B20" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D20" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B21" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D21" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B22" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D22" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B23" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D23" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B24" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D24" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B25" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D25" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B26" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D26" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>544</v>
+      </c>
+      <c r="B27" t="s">
+        <v>613</v>
+      </c>
+      <c r="D27" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>545</v>
       </c>
-      <c r="B27" t="s">
-        <v>614</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="B28" t="s">
+        <v>608</v>
+      </c>
+      <c r="D28" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>546</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
+        <v>613</v>
+      </c>
+      <c r="D29" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>547</v>
+      </c>
+      <c r="B30" t="s">
+        <v>608</v>
+      </c>
+      <c r="D30" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>548</v>
+      </c>
+      <c r="B31" t="s">
         <v>609</v>
-      </c>
-      <c r="D28" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>547</v>
-      </c>
-      <c r="B29" t="s">
-        <v>614</v>
-      </c>
-      <c r="D29" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>548</v>
-      </c>
-      <c r="B30" t="s">
-        <v>609</v>
-      </c>
-      <c r="D30" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>549</v>
-      </c>
-      <c r="B31" t="s">
-        <v>610</v>
       </c>
       <c r="D31" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>549</v>
+      </c>
+      <c r="B32" t="s">
+        <v>609</v>
+      </c>
+      <c r="D32" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>550</v>
       </c>
-      <c r="B32" t="s">
-        <v>610</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="B33" t="s">
+        <v>609</v>
+      </c>
+      <c r="D33" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>551</v>
       </c>
-      <c r="B33" t="s">
-        <v>610</v>
-      </c>
-      <c r="D33" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>552</v>
-      </c>
       <c r="B34" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D34" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B35" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D35" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>553</v>
+      </c>
+      <c r="B36" t="s">
+        <v>608</v>
+      </c>
+      <c r="D36" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>554</v>
       </c>
-      <c r="B36" t="s">
-        <v>609</v>
-      </c>
-      <c r="D36" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>555</v>
-      </c>
       <c r="B37" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D37" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>555</v>
+      </c>
+      <c r="B38" t="s">
+        <v>607</v>
+      </c>
+      <c r="D38" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>556</v>
       </c>
-      <c r="B38" t="s">
-        <v>608</v>
-      </c>
-      <c r="D38" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>557</v>
-      </c>
       <c r="B39" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D39" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>557</v>
+      </c>
+      <c r="B40" t="s">
+        <v>608</v>
+      </c>
+      <c r="D40" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>558</v>
       </c>
-      <c r="B40" t="s">
-        <v>609</v>
-      </c>
-      <c r="D40" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>559</v>
-      </c>
       <c r="B41" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D41" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>559</v>
+      </c>
+      <c r="B42" t="s">
+        <v>616</v>
+      </c>
+      <c r="D42" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>560</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
+        <v>609</v>
+      </c>
+      <c r="D43" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>561</v>
+      </c>
+      <c r="B44" t="s">
         <v>617</v>
-      </c>
-      <c r="D42" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>561</v>
-      </c>
-      <c r="B43" t="s">
-        <v>610</v>
-      </c>
-      <c r="D43" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>562</v>
-      </c>
-      <c r="B44" t="s">
-        <v>618</v>
       </c>
       <c r="D44" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B45" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D45" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B46" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D46" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B47" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D47" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B48" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D48" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>566</v>
+      </c>
+      <c r="B49" t="s">
+        <v>620</v>
+      </c>
+      <c r="D49" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>567</v>
       </c>
-      <c r="B49" t="s">
-        <v>621</v>
-      </c>
-      <c r="D49" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>568</v>
-      </c>
       <c r="B50" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D50" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B51" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D51" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B52" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D52" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B53" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D53" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>571</v>
+      </c>
+      <c r="B54" t="s">
+        <v>620</v>
+      </c>
+      <c r="D54" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>572</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
+        <v>620</v>
+      </c>
+      <c r="D55" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>573</v>
+      </c>
+      <c r="B56" t="s">
         <v>621</v>
       </c>
-      <c r="D54" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>573</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="D56" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>574</v>
+      </c>
+      <c r="B57" t="s">
         <v>621</v>
       </c>
-      <c r="D55" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>574</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="D57" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>575</v>
+      </c>
+      <c r="B58" t="s">
         <v>622</v>
-      </c>
-      <c r="D56" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>575</v>
-      </c>
-      <c r="B57" t="s">
-        <v>622</v>
-      </c>
-      <c r="D57" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>576</v>
-      </c>
-      <c r="B58" t="s">
-        <v>623</v>
       </c>
       <c r="D58" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B59" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D59" t="s">
         <v>182</v>
@@ -11061,7 +11122,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D208FD11-3A3C-4357-9FF7-ED2CAF88E4C2}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
